--- a/Excel/14_Electricity_Scope2_WIP_v02.xlsx
+++ b/Excel/14_Electricity_Scope2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8013309D-5381-48B8-A506-3B26B735A5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A1EAF4-C5C2-41CF-829B-2D8D67A18BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="465" windowWidth="35745" windowHeight="18900" firstSheet="2" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1755" yWindow="1020" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -269,6 +269,7 @@
     <definedName name="X_Cell_Electricity_Market_AmountPurchasedGreenPower">'Input - Electricity'!$E$27</definedName>
     <definedName name="X_Cell_Electricity_Market_JurisdictionalRenewablePowerPercentage">'Input - Electricity'!$E$25</definedName>
     <definedName name="X_Cell_Electricity_Market_RenewablePowerPercentage">'Input - Electricity'!$E$24</definedName>
+    <definedName name="X_Cell_Site_EndDate">'Input - Site'!$E$13</definedName>
     <definedName name="X_Cell_Site_FarmName">'Input - Site'!$E$7</definedName>
     <definedName name="X_Cell_Site_Region">'Input - Site'!$E$22</definedName>
     <definedName name="X_Cell_Site_ReportingEntityName">'Input - Site'!$E$8</definedName>
@@ -8171,7 +8172,7 @@
         <v>91</v>
       </c>
       <c r="E16" s="29" t="str">
-        <f>IF('Input - Site'!E21="Western Australia", 'Input - Site'!E22, 'Input - Site'!E21)</f>
+        <f>IF(X_Cell_Site_State="Western Australia", X_Cell_Site_Region, X_Cell_Site_State)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
       <c r="F16" s="19"/>
@@ -8265,7 +8266,7 @@
         <v>142</v>
       </c>
       <c r="E29" s="116" t="str">
-        <f>TEXT('Input - Site'!$E$12, "dd mmm yyyy")</f>
+        <f>TEXT('Input - Site'!E12, "dd mmm yyyy")</f>
         <v>01 Jan 2024</v>
       </c>
       <c r="K29" s="49"/>
@@ -8276,7 +8277,7 @@
         <v>127</v>
       </c>
       <c r="E30" s="116" t="str">
-        <f>TEXT('Input - Site'!$E$13, "dd mmm yyyy")</f>
+        <f>TEXT('Input - Site'!E13, "dd mmm yyyy")</f>
         <v>31 Dec 2024</v>
       </c>
       <c r="K30" s="49"/>
@@ -13946,10 +13947,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGEAcwBzAG8AYwBpAGEAdABlAGQAIAB3AGkAdABoACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABhAG4AZAAgAGwAbwBzAHMAZQBzACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAIABhAGMAcQB1AGkAcgBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAAxAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAAwAC4ANwA4ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgADAALgA2ADcALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADAALgAyADIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdAAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABTAFcASQBTACkAXAAiACwAIAAwAC4ANQAwACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAZQByAG4AIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgATgBXAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgADAALgAyADAALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQAgAC0AIABEAGEAcgB3AGkAbgAgAEsAYQB0AGgAZQByAGkAbgBlACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAEQASwBJAFMAKQBcACIALAAgADAALgA1ADYALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4ANgAyACwAIAAwAC4AMAA3AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATgBTAFcAIABhAG4AZAAgAEEAQwBUACAAcwBwAGwAaQB0ACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAHIAbwB3AHMALgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBSAGUAcwBpAGQAdQBhAGwAIABNAGkAeAAgAEYAYQBjAHQAbwByACAAZgBvAHIAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGUAcQB1AGEAdABpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACAAbQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgADIAYQAgAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAcgBvAG0AIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQA6ACAAbQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABmAGEAYwB0AG8AcgBzACAAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADIAYQBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACwAIABUAGUAcgByAGkAdABvAHIAeQAgAG8AcgAgAGcAcgBpAGQAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AXAAiACwAIABcACIAUwBjAG8AcABlACAAMgAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyAC0AZQAvAGsAVwBoACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMgAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAGsAVwBoACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAaQBvAG4AYQBsAFwAIgAsACAAMAAuADgAMQAsACAAMgAyADYALAAgADAALgAxADAALAAgADIAOQBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA0ADoAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEANAAuADEALgAxACAAUAB1AHIAYwBoAGEAcwBlAGQAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAEwAbwBjAGEAdABpAG8AbgAtAEIAYQBzAGUAZAApAFwAbgAxADQALgAxAC4AMgAgAFAAdQByAGMAaABhAHMAZQBkACAARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABNAGEAcgBrAGUAdAAtAEIAYQBzAGUAZAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4ARQBfADIAZQBsAGUAYwBcAG4AdAAgAEMATwAyAGUAXABuAEUAXwB7ADIALABlAGwAZQBjAH0APQBRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAMgAsAGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQBfAGUAbABlAGMAIAA9ACAAYQBtAG8AdQBuAHQAIABvAGYAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAGcAcgBpAGQAIAAoAGsAVwBoACkAXABuAEUARgBfADIAZQBsAGUAYwAgAD0AIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgACgAawBnACAAQwBPADIAZQAvAGsAVwBoACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAEUARgBfADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACAAKgAgAEUARgBfADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMgAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfADIAZQBsAGUAYwBcACIALAAgAFwAIgBsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBXAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAGQAZABlAGQAIABnACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYwBhAHAAdAB1AHIAZQAgAHcAaABpAGMAaAAgAGcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuAE0AYQByAGsAZQB0AC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAF8AMgBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMgAsAGUAbABlAGMAfQA9ACgAKABRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAKQAtACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZAAgACgAawBXAGgAKQBcAG4AUgBQAFAAIAA9ACAAUgBlAG4AZQB3AGEAYgBsAGUAIABQAG8AdwBlAHIAIABQAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAAdABoAGUAIABMAGEAcgBnAGUALQBzAGMAYQBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAVABhAHIAZwBlAHQAIAAoAEwAUgBFAFQAKQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBKAFIAUABQACAAPQAgAGoAdQByAGkAcwBkAGkAYwB0AGkAbwBuAGEAbAAgAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAG8AbgBsAHkAIABhAHAAcABsAGkAZQBzACAAdABvACAAdABoAGUAIABBAEMAVAApACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4AUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABlAGwAaQBnAGkAYgBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABpAG4AIAB0AGgAZQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAeQBlAGEAcgAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAAoAE0AVwBoACkAXABuAFIARQBDAF8AbwBuAHMAaQB0AGUAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABlAGwAaQBnAGkAYgBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB0AGgAYQB0ACAAaABhAHYAZQAgAGIAZQBlAG4AIABvAHIAIAB3AGkAbABsACAAYgBlACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAcgBvAGQAdQBjAGUAZAAgAG8AbgAtAHMAaQB0AGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAeQBlAGEAcgAgAGEAbgBkACAAYwBvAG4AcwB1AG0AZQBkACAAYgB5ACAAdABoAGUAIABlAG4AdABpAHQAeQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAAoAE0AVwBoACkAXABuAEUARgBfAFIATQBGADIAZQBsAGUAYwAgAD0AIABTAGMAbwBwAGUAIAAyACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABrAGcAIABDAE8AMgBlAC8AawBXAGgAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgAC0AMwApACkAIAAqACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgADMAKQApACAAKgAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADQALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAyACwAZQBsAGUAYwB9AD0AKABRAF8AewBlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAKAAxAC0AKABSAFAAUAArAEoAUgBQAFAAKQApACAALQAgACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAKQAgAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADIALABlAGwAZQBjAH0APQAoAFEAXwB7AGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAIAAtACAAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsAMwB9ACkAKQAgAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAUABQAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAUABvAHcAZQByACAAUABlAHIAYwBlAG4AdABhAGcAZQAgAHUAbgBkAGUAcgAgAHQAaABlACAATABhAHIAZwBlAC0AcwBjAGEAbABlACAAUgBlAG4AZQB3AGEAYgBsAGUAIABFAG4AZQByAGcAeQAgAFQAYQByAGcAZQB0ACAAKABMAFIARQBUACkAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBSAFAAUABcACIALAAgAFwAIgBqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkACAAKABBAEMAVAAgAG8AbgBsAHkAKQBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZABcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABpAG4AIAB0AGgAZQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAeQBlAGEAcgBcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AbwBuAHMAaQB0AGUAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABFAG4AZQByAGcAeQAgAEMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAcgBvAGQAdQBjAGUAZAAgAG8AbgAtAHMAaQB0AGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAeQBlAGEAcgAgAGEAbgBkACAAYwBvAG4AcwB1AG0AZQBkACAAYgB5ACAAdABoAGUAIABlAG4AdABpAHQAeQBcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFIATQBGADIAZQBsAGUAYwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAASQBuACAAbwByAGQAZQByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgAHQAbwAgAGsAaQBsAG8AdwBhAHQAdAAgAGgAbwB1AHIAcwAsACAAdABoAGUAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGEAbgBkACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAgAHYAYQByAGkAYQBiAGwAZQBzACAAYQByAGUAIABtAHUAbAB0AGkAcABsAGkAZQBkACAAYgB5ACAAMQAwAF4AMwAgAGkAbgBzAHQAZQBhAGQAIABvAGYAIAAxADAAXgAtADMALgBcACIAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVABpAHQAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGEAdABhACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAVgBhAHIAaQBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -14144,35 +14161,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGEAcwBzAG8AYwBpAGEAdABlAGQAIAB3AGkAdABoACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABhAG4AZAAgAGwAbwBzAHMAZQBzACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAIABhAGMAcQB1AGkAcgBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAAxAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAAwAC4ANwA4ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgADAALgA2ADcALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADAALgAyADIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdAAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABTAFcASQBTACkAXAAiACwAIAAwAC4ANQAwACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAZQByAG4AIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgATgBXAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgADAALgAyADAALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQAgAC0AIABEAGEAcgB3AGkAbgAgAEsAYQB0AGgAZQByAGkAbgBlACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAEQASwBJAFMAKQBcACIALAAgADAALgA1ADYALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4ANgAyACwAIAAwAC4AMAA3AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATgBTAFcAIABhAG4AZAAgAEEAQwBUACAAcwBwAGwAaQB0ACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAHIAbwB3AHMALgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBSAGUAcwBpAGQAdQBhAGwAIABNAGkAeAAgAEYAYQBjAHQAbwByACAAZgBvAHIAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGUAcQB1AGEAdABpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACAAbQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgADIAYQAgAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAcgBvAG0AIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQA6ACAAbQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABmAGEAYwB0AG8AcgBzACAAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADIAYQBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACwAIABUAGUAcgByAGkAdABvAHIAeQAgAG8AcgAgAGcAcgBpAGQAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AXAAiACwAIABcACIAUwBjAG8AcABlACAAMgAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyAC0AZQAvAGsAVwBoACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMgAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAGsAVwBoACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAaQBvAG4AYQBsAFwAIgAsACAAMAAuADgAMQAsACAAMgAyADYALAAgADAALgAxADAALAAgADIAOQBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA0ADoAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEANAAuADEALgAxACAAUAB1AHIAYwBoAGEAcwBlAGQAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAEwAbwBjAGEAdABpAG8AbgAtAEIAYQBzAGUAZAApAFwAbgAxADQALgAxAC4AMgAgAFAAdQByAGMAaABhAHMAZQBkACAARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABNAGEAcgBrAGUAdAAtAEIAYQBzAGUAZAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4ARQBfADIAZQBsAGUAYwBcAG4AdAAgAEMATwAyAGUAXABuAEUAXwB7ADIALABlAGwAZQBjAH0APQBRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAMgAsAGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQBfAGUAbABlAGMAIAA9ACAAYQBtAG8AdQBuAHQAIABvAGYAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAGcAcgBpAGQAIAAoAGsAVwBoACkAXABuAEUARgBfADIAZQBsAGUAYwAgAD0AIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgACgAawBnACAAQwBPADIAZQAvAGsAVwBoACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAEUARgBfADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACAAKgAgAEUARgBfADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMgAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfADIAZQBsAGUAYwBcACIALAAgAFwAIgBsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBXAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAGQAZABlAGQAIABnACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYwBhAHAAdAB1AHIAZQAgAHcAaABpAGMAaAAgAGcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuAE0AYQByAGsAZQB0AC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAF8AMgBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMgAsAGUAbABlAGMAfQA9ACgAKABRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAKQAtACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZAAgACgAawBXAGgAKQBcAG4AUgBQAFAAIAA9ACAAUgBlAG4AZQB3AGEAYgBsAGUAIABQAG8AdwBlAHIAIABQAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAAdABoAGUAIABMAGEAcgBnAGUALQBzAGMAYQBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAVABhAHIAZwBlAHQAIAAoAEwAUgBFAFQAKQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBKAFIAUABQACAAPQAgAGoAdQByAGkAcwBkAGkAYwB0AGkAbwBuAGEAbAAgAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAG8AbgBsAHkAIABhAHAAcABsAGkAZQBzACAAdABvACAAdABoAGUAIABBAEMAVAApACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4AUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABlAGwAaQBnAGkAYgBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABpAG4AIAB0AGgAZQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAeQBlAGEAcgAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAAoAE0AVwBoACkAXABuAFIARQBDAF8AbwBuAHMAaQB0AGUAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABlAGwAaQBnAGkAYgBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB0AGgAYQB0ACAAaABhAHYAZQAgAGIAZQBlAG4AIABvAHIAIAB3AGkAbABsACAAYgBlACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAcgBvAGQAdQBjAGUAZAAgAG8AbgAtAHMAaQB0AGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAeQBlAGEAcgAgAGEAbgBkACAAYwBvAG4AcwB1AG0AZQBkACAAYgB5ACAAdABoAGUAIABlAG4AdABpAHQAeQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAAoAE0AVwBoACkAXABuAEUARgBfAFIATQBGADIAZQBsAGUAYwAgAD0AIABTAGMAbwBwAGUAIAAyACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABrAGcAIABDAE8AMgBlAC8AawBXAGgAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgAC0AMwApACkAIAAqACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgADMAKQApACAAKgAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADQALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAyACwAZQBsAGUAYwB9AD0AKABRAF8AewBlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAKAAxAC0AKABSAFAAUAArAEoAUgBQAFAAKQApACAALQAgACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAKQAgAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADIALABlAGwAZQBjAH0APQAoAFEAXwB7AGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAIAAtACAAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsAMwB9ACkAKQAgAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAUABQAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAUABvAHcAZQByACAAUABlAHIAYwBlAG4AdABhAGcAZQAgAHUAbgBkAGUAcgAgAHQAaABlACAATABhAHIAZwBlAC0AcwBjAGEAbABlACAAUgBlAG4AZQB3AGEAYgBsAGUAIABFAG4AZQByAGcAeQAgAFQAYQByAGcAZQB0ACAAKABMAFIARQBUACkAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBSAFAAUABcACIALAAgAFwAIgBqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkACAAKABBAEMAVAAgAG8AbgBsAHkAKQBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZABcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABpAG4AIAB0AGgAZQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAeQBlAGEAcgBcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AbwBuAHMAaQB0AGUAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABFAG4AZQByAGcAeQAgAEMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAcgBvAGQAdQBjAGUAZAAgAG8AbgAtAHMAaQB0AGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAeQBlAGEAcgAgAGEAbgBkACAAYwBvAG4AcwB1AG0AZQBkACAAYgB5ACAAdABoAGUAIABlAG4AdABpAHQAeQBcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFIATQBGADIAZQBsAGUAYwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAASQBuACAAbwByAGQAZQByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgAHQAbwAgAGsAaQBsAG8AdwBhAHQAdAAgAGgAbwB1AHIAcwAsACAAdABoAGUAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGEAbgBkACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAgAHYAYQByAGkAYQBiAGwAZQBzACAAYQByAGUAIABtAHUAbAB0AGkAcABsAGkAZQBkACAAYgB5ACAAMQAwAF4AMwAgAGkAbgBzAHQAZQBhAGQAIABvAGYAIAAxADAAXgAtADMALgBcACIAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVABpAHQAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGEAdABhACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAVgBhAHIAaQBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14191,21 +14203,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/14_Electricity_Scope2_WIP_v02.xlsx
+++ b/Excel/14_Electricity_Scope2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A1EAF4-C5C2-41CF-829B-2D8D67A18BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323140D9-CA0D-43F6-B4FE-B0BACD623EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1020" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -178,6 +178,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fertiliser type f","FracGASFf","Basis";"Urea-based fertilisers",0.15,"Urea";"Ammonium-based fertilisers",0.08,"Ammonium";"Nitrate-based fertilisers",0.01,"Nitrate";"Ammonium-nitrate based fertilisers",0.05,"Ammonium-nitrate";"Other fertilisers",0.11,"Other"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4 Table 11.3 [1, p. 11]")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Source">_xlfn.LAMBDA("VEERG 2026:Table 12.2.2.9")</definedName>
@@ -13947,15 +13948,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -13966,7 +13958,20 @@
 </p:properties>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGEAcwBzAG8AYwBpAGEAdABlAGQAIAB3AGkAdABoACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABhAG4AZAAgAGwAbwBzAHMAZQBzACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAIABhAGMAcQB1AGkAcgBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAAxAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAAwAC4ANwA4ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgADAALgA2ADcALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADAALgAyADIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdAAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABTAFcASQBTACkAXAAiACwAIAAwAC4ANQAwACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAZQByAG4AIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgATgBXAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgADAALgAyADAALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQAgAC0AIABEAGEAcgB3AGkAbgAgAEsAYQB0AGgAZQByAGkAbgBlACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAEQASwBJAFMAKQBcACIALAAgADAALgA1ADYALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4ANgAyACwAIAAwAC4AMAA3AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATgBTAFcAIABhAG4AZAAgAEEAQwBUACAAcwBwAGwAaQB0ACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAHIAbwB3AHMALgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBSAGUAcwBpAGQAdQBhAGwAIABNAGkAeAAgAEYAYQBjAHQAbwByACAAZgBvAHIAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGUAcQB1AGEAdABpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACAAbQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgADIAYQAgAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAcgBvAG0AIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQA6ACAAbQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABmAGEAYwB0AG8AcgBzACAAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADIAYQBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACwAIABUAGUAcgByAGkAdABvAHIAeQAgAG8AcgAgAGcAcgBpAGQAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AXAAiACwAIABcACIAUwBjAG8AcABlACAAMgAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyAC0AZQAvAGsAVwBoACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMgAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAGsAVwBoACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAaQBvAG4AYQBsAFwAIgAsACAAMAAuADgAMQAsACAAMgAyADYALAAgADAALgAxADAALAAgADIAOQBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA0ADoAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEANAAuADEALgAxACAAUAB1AHIAYwBoAGEAcwBlAGQAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAEwAbwBjAGEAdABpAG8AbgAtAEIAYQBzAGUAZAApAFwAbgAxADQALgAxAC4AMgAgAFAAdQByAGMAaABhAHMAZQBkACAARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABNAGEAcgBrAGUAdAAtAEIAYQBzAGUAZAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4ARQBfADIAZQBsAGUAYwBcAG4AdAAgAEMATwAyAGUAXABuAEUAXwB7ADIALABlAGwAZQBjAH0APQBRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAMgAsAGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQBfAGUAbABlAGMAIAA9ACAAYQBtAG8AdQBuAHQAIABvAGYAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAGcAcgBpAGQAIAAoAGsAVwBoACkAXABuAEUARgBfADIAZQBsAGUAYwAgAD0AIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgACgAawBnACAAQwBPADIAZQAvAGsAVwBoACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAEUARgBfADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACAAKgAgAEUARgBfADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMgAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfADIAZQBsAGUAYwBcACIALAAgAFwAIgBsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBXAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAGQAZABlAGQAIABnACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYwBhAHAAdAB1AHIAZQAgAHcAaABpAGMAaAAgAGcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuAE0AYQByAGsAZQB0AC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAF8AMgBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMgAsAGUAbABlAGMAfQA9ACgAKABRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAKQAtACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZAAgACgAawBXAGgAKQBcAG4AUgBQAFAAIAA9ACAAUgBlAG4AZQB3AGEAYgBsAGUAIABQAG8AdwBlAHIAIABQAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAAdABoAGUAIABMAGEAcgBnAGUALQBzAGMAYQBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAVABhAHIAZwBlAHQAIAAoAEwAUgBFAFQAKQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBKAFIAUABQACAAPQAgAGoAdQByAGkAcwBkAGkAYwB0AGkAbwBuAGEAbAAgAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAG8AbgBsAHkAIABhAHAAcABsAGkAZQBzACAAdABvACAAdABoAGUAIABBAEMAVAApACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4AUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABlAGwAaQBnAGkAYgBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABpAG4AIAB0AGgAZQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAeQBlAGEAcgAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAAoAE0AVwBoACkAXABuAFIARQBDAF8AbwBuAHMAaQB0AGUAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABlAGwAaQBnAGkAYgBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB0AGgAYQB0ACAAaABhAHYAZQAgAGIAZQBlAG4AIABvAHIAIAB3AGkAbABsACAAYgBlACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAcgBvAGQAdQBjAGUAZAAgAG8AbgAtAHMAaQB0AGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAeQBlAGEAcgAgAGEAbgBkACAAYwBvAG4AcwB1AG0AZQBkACAAYgB5ACAAdABoAGUAIABlAG4AdABpAHQAeQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAAoAE0AVwBoACkAXABuAEUARgBfAFIATQBGADIAZQBsAGUAYwAgAD0AIABTAGMAbwBwAGUAIAAyACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABrAGcAIABDAE8AMgBlAC8AawBXAGgAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgAC0AMwApACkAIAAqACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgADMAKQApACAAKgAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADQALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAyACwAZQBsAGUAYwB9AD0AKABRAF8AewBlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAKAAxAC0AKABSAFAAUAArAEoAUgBQAFAAKQApACAALQAgACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAKQAgAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADIALABlAGwAZQBjAH0APQAoAFEAXwB7AGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAIAAtACAAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsAMwB9ACkAKQAgAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAUABQAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAUABvAHcAZQByACAAUABlAHIAYwBlAG4AdABhAGcAZQAgAHUAbgBkAGUAcgAgAHQAaABlACAATABhAHIAZwBlAC0AcwBjAGEAbABlACAAUgBlAG4AZQB3AGEAYgBsAGUAIABFAG4AZQByAGcAeQAgAFQAYQByAGcAZQB0ACAAKABMAFIARQBUACkAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBSAFAAUABcACIALAAgAFwAIgBqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkACAAKABBAEMAVAAgAG8AbgBsAHkAKQBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZABcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABpAG4AIAB0AGgAZQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAeQBlAGEAcgBcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AbwBuAHMAaQB0AGUAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABFAG4AZQByAGcAeQAgAEMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAcgBvAGQAdQBjAGUAZAAgAG8AbgAtAHMAaQB0AGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAeQBlAGEAcgAgAGEAbgBkACAAYwBvAG4AcwB1AG0AZQBkACAAYgB5ACAAdABoAGUAIABlAG4AdABpAHQAeQBcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFIATQBGADIAZQBsAGUAYwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAASQBuACAAbwByAGQAZQByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgAHQAbwAgAGsAaQBsAG8AdwBhAHQAdAAgAGgAbwB1AHIAcwAsACAAdABoAGUAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGEAbgBkACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAgAHYAYQByAGkAYQBiAGwAZQBzACAAYQByAGUAIABtAHUAbAB0AGkAcABsAGkAZQBkACAAYgB5ACAAMQAwAF4AMwAgAGkAbgBzAHQAZQBhAGQAIABvAGYAIAAxADAAXgAtADMALgBcACIAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVABpAHQAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGEAdABhACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAVgBhAHIAaQBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -14161,19 +14166,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGEAcwBzAG8AYwBpAGEAdABlAGQAIAB3AGkAdABoACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABhAG4AZAAgAGwAbwBzAHMAZQBzACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAIABhAGMAcQB1AGkAcgBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAAxAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAAwAC4ANwA4ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgADAALgA2ADcALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADAALgAyADIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdAAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABTAFcASQBTACkAXAAiACwAIAAwAC4ANQAwACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAZQByAG4AIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgATgBXAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgADAALgAyADAALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQAgAC0AIABEAGEAcgB3AGkAbgAgAEsAYQB0AGgAZQByAGkAbgBlACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAEQASwBJAFMAKQBcACIALAAgADAALgA1ADYALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4ANgAyACwAIAAwAC4AMAA3AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATgBTAFcAIABhAG4AZAAgAEEAQwBUACAAcwBwAGwAaQB0ACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAHIAbwB3AHMALgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBSAGUAcwBpAGQAdQBhAGwAIABNAGkAeAAgAEYAYQBjAHQAbwByACAAZgBvAHIAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGUAcQB1AGEAdABpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACAAbQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgADIAYQAgAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAcgBvAG0AIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQA6ACAAbQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABmAGEAYwB0AG8AcgBzACAAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADIAYQBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACwAIABUAGUAcgByAGkAdABvAHIAeQAgAG8AcgAgAGcAcgBpAGQAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AXAAiACwAIABcACIAUwBjAG8AcABlACAAMgAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyAC0AZQAvAGsAVwBoACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMgAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAGsAVwBoACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAaQBvAG4AYQBsAFwAIgAsACAAMAAuADgAMQAsACAAMgAyADYALAAgADAALgAxADAALAAgADIAOQBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA0ADoAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEANAAuADEALgAxACAAUAB1AHIAYwBoAGEAcwBlAGQAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAEwAbwBjAGEAdABpAG8AbgAtAEIAYQBzAGUAZAApAFwAbgAxADQALgAxAC4AMgAgAFAAdQByAGMAaABhAHMAZQBkACAARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABNAGEAcgBrAGUAdAAtAEIAYQBzAGUAZAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4ARQBfADIAZQBsAGUAYwBcAG4AdAAgAEMATwAyAGUAXABuAEUAXwB7ADIALABlAGwAZQBjAH0APQBRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAMgAsAGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQBfAGUAbABlAGMAIAA9ACAAYQBtAG8AdQBuAHQAIABvAGYAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAGcAcgBpAGQAIAAoAGsAVwBoACkAXABuAEUARgBfADIAZQBsAGUAYwAgAD0AIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgACgAawBnACAAQwBPADIAZQAvAGsAVwBoACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAEUARgBfADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACAAKgAgAEUARgBfADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMgAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfADIAZQBsAGUAYwBcACIALAAgAFwAIgBsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBXAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAGQAZABlAGQAIABnACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYwBhAHAAdAB1AHIAZQAgAHcAaABpAGMAaAAgAGcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuAE0AYQByAGsAZQB0AC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAF8AMgBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMgAsAGUAbABlAGMAfQA9ACgAKABRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAKQAtACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZAAgACgAawBXAGgAKQBcAG4AUgBQAFAAIAA9ACAAUgBlAG4AZQB3AGEAYgBsAGUAIABQAG8AdwBlAHIAIABQAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAAdABoAGUAIABMAGEAcgBnAGUALQBzAGMAYQBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAVABhAHIAZwBlAHQAIAAoAEwAUgBFAFQAKQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBKAFIAUABQACAAPQAgAGoAdQByAGkAcwBkAGkAYwB0AGkAbwBuAGEAbAAgAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAG8AbgBsAHkAIABhAHAAcABsAGkAZQBzACAAdABvACAAdABoAGUAIABBAEMAVAApACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4AUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABlAGwAaQBnAGkAYgBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABpAG4AIAB0AGgAZQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAeQBlAGEAcgAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAAoAE0AVwBoACkAXABuAFIARQBDAF8AbwBuAHMAaQB0AGUAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABlAGwAaQBnAGkAYgBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB0AGgAYQB0ACAAaABhAHYAZQAgAGIAZQBlAG4AIABvAHIAIAB3AGkAbABsACAAYgBlACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAcgBvAGQAdQBjAGUAZAAgAG8AbgAtAHMAaQB0AGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAeQBlAGEAcgAgAGEAbgBkACAAYwBvAG4AcwB1AG0AZQBkACAAYgB5ACAAdABoAGUAIABlAG4AdABpAHQAeQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAAoAE0AVwBoACkAXABuAEUARgBfAFIATQBGADIAZQBsAGUAYwAgAD0AIABTAGMAbwBwAGUAIAAyACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABrAGcAIABDAE8AMgBlAC8AawBXAGgAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgAC0AMwApACkAIAAqACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgADMAKQApACAAKgAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADQALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAyACwAZQBsAGUAYwB9AD0AKABRAF8AewBlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAKAAxAC0AKABSAFAAUAArAEoAUgBQAFAAKQApACAALQAgACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAKQAgAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADIALABlAGwAZQBjAH0APQAoAFEAXwB7AGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAIAAtACAAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsAMwB9ACkAKQAgAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAUABQAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAUABvAHcAZQByACAAUABlAHIAYwBlAG4AdABhAGcAZQAgAHUAbgBkAGUAcgAgAHQAaABlACAATABhAHIAZwBlAC0AcwBjAGEAbABlACAAUgBlAG4AZQB3AGEAYgBsAGUAIABFAG4AZQByAGcAeQAgAFQAYQByAGcAZQB0ACAAKABMAFIARQBUACkAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBSAFAAUABcACIALAAgAFwAIgBqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkACAAKABBAEMAVAAgAG8AbgBsAHkAKQBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZABcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABpAG4AIAB0AGgAZQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAeQBlAGEAcgBcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AbwBuAHMAaQB0AGUAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABFAG4AZQByAGcAeQAgAEMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAcgBvAGQAdQBjAGUAZAAgAG8AbgAtAHMAaQB0AGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAeQBlAGEAcgAgAGEAbgBkACAAYwBvAG4AcwB1AG0AZQBkACAAYgB5ACAAdABoAGUAIABlAG4AdABpAHQAeQBcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFIATQBGADIAZQBsAGUAYwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAASQBuACAAbwByAGQAZQByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgAHQAbwAgAGsAaQBsAG8AdwBhAHQAdAAgAGgAbwB1AHIAcwAsACAAdABoAGUAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGEAbgBkACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAgAHYAYQByAGkAYQBiAGwAZQBzACAAYQByAGUAIABtAHUAbAB0AGkAcABsAGkAZQBkACAAYgB5ACAAMQAwAF4AMwAgAGkAbgBzAHQAZQBhAGQAIABvAGYAIAAxADAAXgAtADMALgBcACIAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVABpAHQAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGEAdABhACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAVgBhAHIAaQBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -14184,7 +14177,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14201,12 +14210,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/14_Electricity_Scope2_WIP_v02.xlsx
+++ b/Excel/14_Electricity_Scope2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323140D9-CA0D-43F6-B4FE-B0BACD623EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDA4AA0-669D-4B0D-BA79-CA098AA221D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,8 +20,11 @@
     <sheet name="Input - Electricity" sheetId="70" r:id="rId5"/>
     <sheet name="14.1.1-2 Purchased electricity" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Electricity" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="125" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="126" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -2242,176 +2245,6 @@
     <cellStyle name="Variable type other" xfId="63" xr:uid="{6646F6F7-E4F9-4165-8015-E25083532B5B}"/>
   </cellStyles>
   <dxfs count="68">
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3273,6 +3106,176 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5435,6 +5438,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5526,16 +5549,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{0EB1895C-9E8C-4AF2-9E00-D6B27B0AC47D}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1C91172D-A190-4526-AF81-49F1D42FA3C6}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{01803246-E4E7-4C12-9CED-FFEFC9C0B63F}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{36E458F4-4187-4472-BCEB-8259ABB56D95}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C807759-03A6-4EA9-A3A8-2AE252F48040}" name="Wet or Dry Zone" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{1E9D048F-C654-4327-9D9E-81A9B913B4FE}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5544,7 +5567,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{511B8BA5-AF9B-4E90-8B77-F474961E5353}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3D4D21BD-7160-4BD1-BDC9-AA4D0C6E796B}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5552,16 +5575,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BDF12359-4A77-42FA-90A4-CD462B7A32D5}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{DD96F4DC-FCCC-40BF-97CF-4B57609D1040}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{05821D49-3078-4C26-8CEF-1FF0B81C6838}" name="MAT">
+    <tableColumn id="2" xr3:uid="{262ADC43-FC39-4A25-AAF7-D481E9FA0633}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{85F0EB47-3E26-4081-A01B-790F8F5CC68D}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{755FDB7D-D062-4201-A414-EB162DDE34C2}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A23E9FF0-621A-46DB-AF37-618721632CEB}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{AB291061-0A75-4998-BCAD-AF06CFBF900E}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5570,7 +5593,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{FF9DBA8C-B8CD-451B-B149-E05E843AADC7}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{9515D037-A997-4111-8200-B2CE963839E1}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5578,16 +5601,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B40E371A-E30C-4D44-9493-C4F0EC94E5A2}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{538DE9A3-27B5-4162-961C-4DF76768A807}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{779E8154-16A3-4D17-86C3-715AC14DE8F0}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{AA0F4A4D-B90D-4532-B6B4-519286B6D5EA}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{27F5D161-20D8-4A2C-B622-9C1ED7C8161C}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{55D08CC0-B7A7-4600-B121-C5790D8616D0}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B7EF2610-84CC-454C-ADE9-87A434852E68}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{39EC0954-05EE-4353-A4AB-8602A371D94B}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5596,16 +5619,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{5B4BE869-BD2D-4CB6-8F94-4C6FDFB0181F}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{F0E9FE68-57AA-4B53-B001-6DDBCD7A7879}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B6792D08-4CD9-4957-866D-CD24AC220047}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{12F71444-3408-4591-B72F-2319512461FA}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4D8A101F-2F9D-48F4-9D0A-52C7A788BFA9}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{2A0D501C-ADE8-4FE5-AE61-F36450BE4683}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5614,16 +5637,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{77B5BA89-C80A-47F2-A8B6-ED4B582A1C9C}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3D823E7A-0E7A-4D72-B430-F7C185190FF4}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2F4FC8BB-B5E7-4221-86E1-4FA411077C77}" name="Data source">
+    <tableColumn id="1" xr3:uid="{C89C0117-D133-4F2D-81C2-94049D33B129}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1CB283B2-6604-49C4-AD0B-13E9602B0421}" name="Data score">
+    <tableColumn id="2" xr3:uid="{27B7D1D5-DB8B-414F-BDAC-2EC7FABDDEE9}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5632,16 +5655,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{2AEE2770-646A-43B3-B7B5-D9446C498E1F}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{3DE7A940-A9C7-4DBE-81E2-39FBA5A0A31C}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F906496D-A444-4250-8922-433A11D3B881}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{2B569132-4231-4B8D-BF98-593C48D39D92}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{878DA8B7-C630-4AB9-8C95-90F444A5D738}" name="FracWET" dataDxfId="36">
+    <tableColumn id="2" xr3:uid="{B95425A4-B5DC-4C33-A446-028C6B30D1DB}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5650,7 +5673,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{5F2CF032-D7F2-4844-ACBE-EFAB422E543F}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{1317C109-2EB7-4577-968C-965E5DA4773B}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5659,19 +5682,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D0807DD-6AA3-4428-AB95-96AA52AB5C1D}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{D912E879-1BEE-4D12-BBED-A4AC1A965A5E}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8FCA39AD-469E-4CD3-80A6-3C5099BC6238}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{C186B542-E23F-4D37-935E-D2A54A169E5F}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7F5F1FED-030A-4162-A69C-E39984CC7BDC}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{6C010B63-3917-4052-BECE-44F6FC77D23F}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AAB52485-33EF-46FC-9F4B-36BDA871301C}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{AA018E8B-CB7C-4242-8400-7B9C8365520D}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FF942727-9CF7-4E83-B62C-E3D00A8D558C}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{88B10D39-94B9-433A-B409-429FFD31DE9C}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5680,16 +5703,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{082E5E6E-359C-40E3-A8D2-658EDE7A0FAC}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{F442E8BA-BA2C-4E11-A1F1-E6B0087384DF}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6814AD1A-7016-44E0-9C99-03FF83468F83}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{4FFF1876-91BC-4BAB-9FBB-63E0CCEB55E0}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFA1116F-C725-4B55-9B70-E01F18D7D64D}" name="FracWET" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7C216B29-7E6F-4AB3-98EE-7C90F65C313F}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5698,16 +5721,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{F5B896D3-D18E-4B82-B16D-832D4CAA1995}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{DFC4D39D-F4F0-4387-8981-56E2D578990D}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A6E8A000-CB3A-4589-A633-510CB794A021}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{325F428E-97D1-4236-9B8F-2900CECE4B32}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{91A37728-9D03-42EE-883F-34C68FDE0991}" name="EFPRP" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2179DE71-AFD0-4000-9BDE-481D62EAEFB1}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5716,16 +5739,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{84600146-C8D5-41EF-B31F-A7FCF6202E58}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{37077460-6158-4309-AE1E-0A17D6C49270}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{873729FE-B0B8-43E5-88AE-8D20F76416C4}" name="Month">
+    <tableColumn id="1" xr3:uid="{42195ADF-B33E-43A2-AA19-1C520E4F2E62}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4C2B80B-A079-4091-9A9A-9B58521D39CA}" name="Season" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D68D1EB5-6320-45AF-97CE-7027A3EC8A63}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5762,7 +5785,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{DD97BDBB-20B1-4018-B059-7F2FC8F608C2}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{6F87E03A-C267-4420-9EDD-58F98BBA322F}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5782,52 +5805,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{DC67277F-0CDC-427E-9644-E5596A7F4494}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{1C7087C7-B462-43D9-A7A1-4EAECE4EF690}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{45D33B11-136F-44DC-920F-653DE287B84F}" name="MAT (ºC)" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1F8127CC-4664-4427-8B89-7D784FFAC935}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B78AD67B-4603-44F8-AA5D-4C3A9CDD0A62}" name="Anaerobic lagoon" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{81251917-8371-488F-9B02-6A8141CC2E05}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0583BDDD-1635-4862-BADC-97F1690AFE48}" name="Digester / covered lagoons" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{79D84C04-2296-4E4F-AC89-675E82A48195}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F809273A-73C8-40D4-9C50-F2D5C93DEE56}" name="Liquid systems" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{D4EA1C5B-F74C-4A77-A4A9-779B718C8E32}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00449008-A3E7-4114-B413-65EB97C892A9}" name="Daily spread" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{665080C0-AAE6-4CC7-BD40-FB3899CF8CCB}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2758521E-4AF2-4F97-9BD8-45186E981572}" name="Composting (passive windrow)" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{80CC931F-0E69-43D1-8612-1F3448C3660F}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D0A95670-DDCD-45AC-9636-5330B17C3937}" name="Solid storage" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{469E6777-05FE-4211-A01B-967BAFC01452}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F969F9D4-6A52-406A-879A-DB1CBD98D2A6}" name="Pit storage" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{647A4AAA-B1DD-47BB-B7A0-9A28F8A057CA}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1131A76B-25CC-4D1D-ACF4-DE2010E0B5D0}" name="Deep litter" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{90C66CEB-A9FB-4865-BDC8-D7786B07A8D3}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{B570B9BE-F6E9-4755-A835-3AEDA6FE5D89}" name="Poultry manure with bedding" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{2C8FB01D-DA3B-45BB-9F54-B6B382D53855}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{290F1253-0E30-47CF-986A-587171B375E4}" name="Poultry manure without bedding" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{EDC81F35-B339-46F6-8582-8BABE491E7D3}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B4AB0FB4-EB82-415D-9571-BA6462BBB4A8}" name="Direct processing" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{DA72AC50-786C-4789-9830-9CB81B43FBF1}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{A3CFDE98-4294-455E-B95C-7948165A6283}" name="Direct application" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{8ADA3FCD-CE52-430C-8897-8B2F5379EBA5}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{077C2B6B-A9ED-4CEF-A0D5-977191F456F7}" name="Pasture range and paddock" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{5679F4BF-5B38-4C96-ACF2-E6AD5E082465}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{8B0D34FB-6534-4647-9CA2-FF689189ADC8}" name="MAT raw" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{CB1C9779-B465-4B56-A215-28D214F650F1}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5836,16 +5859,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{3777A1D9-9AB6-4A99-9843-98D8910F3861}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{F0A1C1B7-6151-446F-BC07-E4CA929B278D}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{90353079-6C94-4374-B3F7-E6CEFC89A25E}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{097E74B0-21EF-4C6A-81C8-F36204B57AEA}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{62DF64D2-D979-40F8-9AB6-D16FDA4EAAAD}" name="EFNi &amp; EFN2Oi" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{37BF67D8-D719-4D0B-A6AD-1E171A212315}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5906,20 +5929,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2D45D258-076A-4B5A-AA6B-C49DFA191D56}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1E52A99D-2A16-47C5-B5DE-3E545EB57413}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{795177ED-1EBA-43C6-9498-92077FE04B20}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{AC11A64C-3FBC-468E-B939-F5C855F173A4}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E6772BFB-AA6A-41FC-BD6C-C9E793BB4773}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{B4D0AE9E-DFA6-40F6-B60F-AAB5F1B9ED29}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F56D49FB-4059-499C-A541-DB617EE84BCF}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{BE7DD25E-A7B6-4322-993F-5019FCBF1894}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5928,12 +5951,12 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4AF5C838-87E8-4D7B-A7BB-621E19D72D16}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{84D8F464-425B-4CFB-8157-CE34DB6DC5F7}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{D87A9820-7D5C-4E3B-9FDA-0760A549099D}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{39194284-C283-4B1E-B27D-939A14C3665F}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5942,16 +5965,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{6CEEA0DB-3426-4FC4-9C05-FC16BB4DB114}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1AA18832-A6CE-4390-AD94-78D0BC0D2ECE}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{449CE4B5-C92A-4D75-AD48-7B18A369707C}" name="Gas">
+    <tableColumn id="1" xr3:uid="{98057B67-9734-4328-9236-810DFB4D1014}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6207AA7D-D9A5-4D47-B8E9-BAB69025D4FE}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{0D614BB9-6CA3-49C5-9DE9-711083A17F56}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5960,7 +5983,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{E4C15A35-8E09-4760-B0A3-618AB40690CB}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4C084481-A30B-47C6-BA75-0A7C8BB676FB}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5969,19 +5992,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C52D27CF-AD7B-42B7-B36E-CFB70CF6CB19}" name="Gas">
+    <tableColumn id="1" xr3:uid="{7D58DF5F-8927-46FF-981D-879830A90573}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{303926E1-9540-448E-BD4A-87D980C3A4AC}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{02709203-EF59-4CA0-941E-A974D34C1026}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6B00D6B4-3A7A-40A7-8FDE-B4C76D5AE8B2}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{594CF733-99E0-4CB7-A410-882637753ED1}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E2935796-0188-45BB-81D5-45675D22D87B}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{5E193D03-9BE6-4BE9-A59E-0EBC8657E396}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C129806A-705C-4D9D-807B-FDF830B070C7}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{083F510C-6261-4211-86E1-A01986E873C6}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5990,7 +6013,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{1DC25208-F11F-41FC-A971-293EC942CEA7}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D5DC7FE5-F74F-4D8E-AA1E-C71AA8CFEE7F}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6010,52 +6033,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{70C65BBD-65EB-401C-841C-2F90C27F1229}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{6BA3AD44-ACBE-4644-A92F-5FC71FC237EA}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{04F52095-F2E8-4CFF-BC02-735327398AE7}" name="MAT" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{72F1645A-787D-4145-9FC3-BF4411E19E07}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{293C01F0-58C5-4225-B1BF-0AF76DD11236}" name="MAP" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{E9ABD992-0246-4394-9BF8-1E49E3AE3C0F}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{589D5993-98E6-4F10-8BEF-F4D3384D2A1A}" name="Frost days per year" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{F171E21B-CC7B-4E49-AC46-757DC8B21A35}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{406FCB98-F580-476B-8094-37A732C5209C}" name="Elevation" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{E7D65B18-7D7B-4118-BEF8-93088B8CBF85}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{7AA1A242-2BD3-4A2A-9FF2-041A49F70FC5}" name="MAP:PET" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{CDFD0BAB-9E03-4B36-B23A-88A5242452D6}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{FD90A26C-F6B4-4CA9-BFD9-37F32B561D34}" name="Min temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{0E1CFFF6-3DB6-4AC5-9C74-9F9D223502CF}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F2BE60C6-21D0-4D92-962B-F8714AA70957}" name="Max temp" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{6F12C6E7-8816-41A2-937F-F82FFCDB9446}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{9483392B-977A-4443-87CA-3F71C94B91EE}" name="Min rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{966E2354-F061-464E-BC29-988BE9BEA0A9}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{66A31397-B101-451A-AFF2-657EEC54BB8A}" name="Max rainfall" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{DE8304D5-7AC5-49AD-9CF5-0122B9813D35}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{76E99937-B5E0-46CF-8F37-854ABC92A2CE}" name="Min frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{396701DB-621F-41F5-8581-149AF540D3E0}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{79453B92-681F-4F2C-A55A-6A70BFA2A296}" name="Max frost days" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{FC278AD2-9E30-41DB-83B1-14F92C3BA27C}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{241623C7-2535-40B3-98B6-CB4E146DC870}" name="Min elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{37B3BDA5-B646-43FB-ADA6-A99DA90CC892}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{01C0BA39-A5B7-4660-87AF-2141015EE601}" name="Max elevation" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{6DAFF6E8-C962-4332-B4B8-1F011653A00D}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{3B44E29E-E339-424C-9EF8-8294D5D9D33A}" name="Min MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{B7332DDD-FAC4-4C56-A188-03FAA81B2BA5}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{376D0424-4DC1-4C50-81D5-DF1A20DAAAAB}" name="Max MAP:PET" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{5A9ABF7F-9E59-46B2-A502-FCBB6598DDCB}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8665,87 +8688,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F130:F131">
-    <cfRule type="cellIs" dxfId="16" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F143">
-    <cfRule type="cellIs" dxfId="15" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F154:F155">
-    <cfRule type="cellIs" dxfId="14" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F167">
-    <cfRule type="cellIs" dxfId="13" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F254:F255">
-    <cfRule type="cellIs" dxfId="12" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F259:F260">
-    <cfRule type="cellIs" dxfId="11" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F264:F265">
-    <cfRule type="cellIs" dxfId="10" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F288:F289">
-    <cfRule type="cellIs" dxfId="9" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F293:F294">
-    <cfRule type="cellIs" dxfId="8" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F298:F299">
-    <cfRule type="cellIs" dxfId="7" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I59:I63">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67 I126">
-    <cfRule type="cellIs" dxfId="5" priority="74" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="74" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I78:I80">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I84:I87">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I91:I95">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J35 I49:I50 H51:H53 I52 I54:I55 I206 I212 E214:G214">
-    <cfRule type="cellIs" dxfId="1" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J39 I40 J41 I43">
-    <cfRule type="cellIs" dxfId="0" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9956,7 +9979,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{235791DA-4C9F-4E69-8908-19D0D65BC2E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4049A772-9457-4A76-B2C2-E44B01198C50}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13948,6 +13971,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -13958,20 +13990,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGEAcwBzAG8AYwBpAGEAdABlAGQAIAB3AGkAdABoACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABhAG4AZAAgAGwAbwBzAHMAZQBzACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAIABhAGMAcQB1AGkAcgBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAAxAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAAwAC4ANwA4ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgADAALgA2ADcALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADAALgAyADIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdAAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABTAFcASQBTACkAXAAiACwAIAAwAC4ANQAwACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAZQByAG4AIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgATgBXAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgADAALgAyADAALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQAgAC0AIABEAGEAcgB3AGkAbgAgAEsAYQB0AGgAZQByAGkAbgBlACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAEQASwBJAFMAKQBcACIALAAgADAALgA1ADYALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4ANgAyACwAIAAwAC4AMAA3AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATgBTAFcAIABhAG4AZAAgAEEAQwBUACAAcwBwAGwAaQB0ACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAHIAbwB3AHMALgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBSAGUAcwBpAGQAdQBhAGwAIABNAGkAeAAgAEYAYQBjAHQAbwByACAAZgBvAHIAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGUAcQB1AGEAdABpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACAAbQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgADIAYQAgAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAcgBvAG0AIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQA6ACAAbQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABmAGEAYwB0AG8AcgBzACAAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADIAYQBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACwAIABUAGUAcgByAGkAdABvAHIAeQAgAG8AcgAgAGcAcgBpAGQAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AXAAiACwAIABcACIAUwBjAG8AcABlACAAMgAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyAC0AZQAvAGsAVwBoACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMgAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAGsAVwBoACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAaQBvAG4AYQBsAFwAIgAsACAAMAAuADgAMQAsACAAMgAyADYALAAgADAALgAxADAALAAgADIAOQBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA0ADoAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEANAAuADEALgAxACAAUAB1AHIAYwBoAGEAcwBlAGQAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAEwAbwBjAGEAdABpAG8AbgAtAEIAYQBzAGUAZAApAFwAbgAxADQALgAxAC4AMgAgAFAAdQByAGMAaABhAHMAZQBkACAARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABNAGEAcgBrAGUAdAAtAEIAYQBzAGUAZAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4ARQBfADIAZQBsAGUAYwBcAG4AdAAgAEMATwAyAGUAXABuAEUAXwB7ADIALABlAGwAZQBjAH0APQBRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAMgAsAGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQBfAGUAbABlAGMAIAA9ACAAYQBtAG8AdQBuAHQAIABvAGYAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAGcAcgBpAGQAIAAoAGsAVwBoACkAXABuAEUARgBfADIAZQBsAGUAYwAgAD0AIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgACgAawBnACAAQwBPADIAZQAvAGsAVwBoACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAEUARgBfADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACAAKgAgAEUARgBfADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMgAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfADIAZQBsAGUAYwBcACIALAAgAFwAIgBsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBXAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAGQAZABlAGQAIABnACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYwBhAHAAdAB1AHIAZQAgAHcAaABpAGMAaAAgAGcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuAE0AYQByAGsAZQB0AC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAF8AMgBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMgAsAGUAbABlAGMAfQA9ACgAKABRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAKQAtACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAKQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZAAgACgAawBXAGgAKQBcAG4AUgBQAFAAIAA9ACAAUgBlAG4AZQB3AGEAYgBsAGUAIABQAG8AdwBlAHIAIABQAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAAdABoAGUAIABMAGEAcgBnAGUALQBzAGMAYQBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAVABhAHIAZwBlAHQAIAAoAEwAUgBFAFQAKQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBKAFIAUABQACAAPQAgAGoAdQByAGkAcwBkAGkAYwB0AGkAbwBuAGEAbAAgAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAG8AbgBsAHkAIABhAHAAcABsAGkAZQBzACAAdABvACAAdABoAGUAIABBAEMAVAApACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4AUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABlAGwAaQBnAGkAYgBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABpAG4AIAB0AGgAZQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAeQBlAGEAcgAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAAoAE0AVwBoACkAXABuAFIARQBDAF8AbwBuAHMAaQB0AGUAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABlAGwAaQBnAGkAYgBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB0AGgAYQB0ACAAaABhAHYAZQAgAGIAZQBlAG4AIABvAHIAIAB3AGkAbABsACAAYgBlACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAcgBvAGQAdQBjAGUAZAAgAG8AbgAtAHMAaQB0AGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAeQBlAGEAcgAgAGEAbgBkACAAYwBvAG4AcwB1AG0AZQBkACAAYgB5ACAAdABoAGUAIABlAG4AdABpAHQAeQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIAB0AG8AIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAAoAE0AVwBoACkAXABuAEUARgBfAFIATQBGADIAZQBsAGUAYwAgAD0AIABTAGMAbwBwAGUAIAAyACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABrAGcAIABDAE8AMgBlAC8AawBXAGgAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgAC0AMwApACkAIAAqACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgADMAKQApACAAKgAgAEUARgBfAFIATQBGADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADQALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAyACwAZQBsAGUAYwB9AD0AKABRAF8AewBlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAKAAxAC0AKABSAFAAUAArAEoAUgBQAFAAKQApACAALQAgACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAKQAgAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADIALABlAGwAZQBjAH0APQAoAFEAXwB7AGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAIAAtACAAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsAMwB9ACkAKQAgAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAUABQAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAUABvAHcAZQByACAAUABlAHIAYwBlAG4AdABhAGcAZQAgAHUAbgBkAGUAcgAgAHQAaABlACAATABhAHIAZwBlAC0AcwBjAGEAbABlACAAUgBlAG4AZQB3AGEAYgBsAGUAIABFAG4AZQByAGcAeQAgAFQAYQByAGcAZQB0ACAAKABMAFIARQBUACkAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBSAFAAUABcACIALAAgAFwAIgBqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkACAAKABBAEMAVAAgAG8AbgBsAHkAKQBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZABcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABpAG4AIAB0AGgAZQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAeQBlAGEAcgBcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AbwBuAHMAaQB0AGUAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABFAG4AZQByAGcAeQAgAEMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAcgBvAGQAdQBjAGUAZAAgAG8AbgAtAHMAaQB0AGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAeQBlAGEAcgAgAGEAbgBkACAAYwBvAG4AcwB1AG0AZQBkACAAYgB5ACAAdABoAGUAIABlAG4AdABpAHQAeQBcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFIATQBGADIAZQBsAGUAYwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAASQBuACAAbwByAGQAZQByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgAHQAbwAgAGsAaQBsAG8AdwBhAHQAdAAgAGgAbwB1AHIAcwAsACAAdABoAGUAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGEAbgBkACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAgAHYAYQByAGkAYQBiAGwAZQBzACAAYQByAGUAIABtAHUAbAB0AGkAcABsAGkAZQBkACAAYgB5ACAAMQAwAF4AMwAgAGkAbgBzAHQAZQBhAGQAIABvAGYAIAAxADAAXgAtADMALgBcACIAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVABpAHQAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBEAGEAdABhACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAVgBhAHIAaQBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -14166,7 +14185,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBJAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADIAIABhAG4AZAAgAHMAYwBvAHAAZQAgADMAKQAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABhAHMAcwBvAGMAaQBhAHQAZQBkACAAdwBpAHQAaAAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQBuAGQAIABsAG8AcwBzAGUAcwAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbwByACAAYQBjAHEAdQBpAHIAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAsACAAVABlAHIAcgBpAHQAbwByAHkAIABvAHIAIABnAHIAaQBkACAAZABlAHMAYwByAGkAcAB0AGkAbwBuAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADIAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAtAGUALwBrAFcAaAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAtAGUALwBrAFcAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMAAuADYANAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADYANAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADAALgA3ADgALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAMAAuADYANwAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAMAAuADIAMgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0ACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAFMAVwBJAFMAKQBcACIALAAgADAALgA1ADAALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABlAHIAbgAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABOAFcASQBTACkAXAAiACwAIAAwAC4ANQA2ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAMAAuADIAMAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAALQAgAEQAYQByAHcAaQBuACAASwBhAHQAaABlAHIAaQBuAGUAIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgARABLAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AGkAbwBuAGEAbABcACIALAAgADAALgA2ADIALAAgADAALgAwADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFIAZQBzAGkAZAB1AGEAbAAgAE0AaQB4ACAARgBhAGMAdABvAHIAIABmAG8AcgAgAG0AYQByAGsAZQB0AC0AYgBhAHMAZQBkACAAZQBxAHUAYQB0AGkAbwBuAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHMAYwBvAHAAZQAgADIAIABhAG4AZAAgAHMAYwBvAHAAZQAgADMAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAAMgBhACAASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgByAG8AbQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbwByACAAYQBjAHEAdQBpAHIAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ADoAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGYAYQBjAHQAbwByAHMAIABcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAMgBhAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAAawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4AOAAxACwAIAAyADIANgAsACAAMAAuADEAMAAsACAAMgA5AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADQAOgAgAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA0AC4AMQAuADEAIABQAHUAcgBjAGgAYQBzAGUAZAAgAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgACgATABvAGMAYQB0AGkAbwBuAC0AQgBhAHMAZQBkACkAXABuADEANAAuADEALgAyACAAUAB1AHIAYwBoAGEAcwBlAGQAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAE0AYQByAGsAZQB0AC0AQgBhAHMAZQBkACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAF8AMgBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMgAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZAAgACgAawBXAGgAKQBcAG4ARQBGAF8AMgBlAGwAZQBjACAAPQAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABrAGcAIABDAE8AMgBlAC8AawBXAGgAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZQBsAGUAYwAsACAARQBGAF8AMgBlAGwAZQBjACwAXABuACAAIAAgACAAUQBfAGUAbABlAGMAIAAqACAARQBGAF8AMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADIAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAyACwAZQBsAGUAYwB9AD0AUQBfAHsAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7ADIALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AMgBlAGwAZQBjAFwAIgAsACAAXAAiAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGUAZAAgAGcAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABjAGEAcAB0AHUAcgBlACAAdwBoAGkAYwBoACAAZwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAEUAXwAyAGUAbABlAGMAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewAyACwAZQBsAGUAYwB9AD0AKAAoAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAKQApAC0AKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkACAAKABrAFcAaAApAFwAbgBSAFAAUAAgAD0AIABSAGUAbgBlAHcAYQBiAGwAZQAgAFAAbwB3AGUAcgAgAFAAZQByAGMAZQBuAHQAYQBnAGUAIAB1AG4AZABlAHIAIAB0AGgAZQAgAEwAYQByAGcAZQAtAHMAYwBhAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABUAGEAcgBnAGUAdAAgACgATABSAEUAVAApACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZAAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAEoAUgBQAFAAIAA9ACAAagB1AHIAaQBzAGQAaQBjAHQAaQBvAG4AYQBsACAAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZAAgACgAbwBuAGwAeQAgAGEAcABwAGwAaQBlAHMAIAB0AG8AIAB0AGgAZQAgAEEAQwBUACkAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGUAbABpAGcAaQBiAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHAAbwByAHQAaQBuAGcAIAB5AGUAYQByACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgACgATQBXAGgAKQBcAG4AUgBFAEMAXwBvAG4AcwBpAHQAZQAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGUAbABpAGcAaQBiAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHQAaABhAHQAIABoAGEAdgBlACAAYgBlAGUAbgAgAG8AcgAgAHcAaQBsAGwAIABiAGUAIABpAHMAcwB1AGUAZAAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAByAG8AZAB1AGMAZQBkACAAbwBuAC0AcwBpAHQAZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIAB5AGUAYQByACAAYQBuAGQAIABjAG8AbgBzAHUAbQBlAGQAIABiAHkAIAB0AGgAZQAgAGUAbgB0AGkAdAB5ACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgACgATQBXAGgAKQBcAG4ARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAPQAgAFMAYwBvAHAAZQAgADIAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAGsAZwAgAEMATwAyAGUALwBrAFcAaAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAALQAzACkAKQAgACoAIABFAEYAXwBSAE0ARgAyAGUAbABlAGMAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAAMwApACkAIAAqACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADIAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANAAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADIALABlAGwAZQBjAH0APQAoAFEAXwB7AGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAIAAtACAAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQApACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMgAsAGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMgAsAGUAbABlAGMAfQA9ACgAUQBfAHsAZQBsAGUAYwB9ACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAKQAgAC0AIAAoACgAUgBFAEMAXwB7AHMAdQByAHIAZQBuAGQAZQByAGUAZAB9AC0AUgBFAEMAXwB7AG8AbgBzAGkAdABlAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AKQApACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMgAsAGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBQAFAAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABQAG8AdwBlAHIAIABQAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAAdABoAGUAIABMAGEAcgBnAGUALQBzAGMAYQBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAVABhAHIAZwBlAHQAIAAoAEwAUgBFAFQAKQBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAFIAUABQAFwAIgAsACAAXAAiAGoAdQByAGkAcwBkAGkAYwB0AGkAbwBuAGEAbAAgAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAEEAQwBUACAAbwBuAGwAeQApAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHAAbwByAHQAaQBuAGcAIAB5AGUAYQByAFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBFAEMAXwBvAG4AcwBpAHQAZQBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIABpAHMAcwB1AGUAZAAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAByAG8AZAB1AGMAZQBkACAAbwBuAC0AcwBpAHQAZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIAB5AGUAYQByACAAYQBuAGQAIABjAG8AbgBzAHUAbQBlAGQAIABiAHkAIAB0AGgAZQAgAGUAbgB0AGkAdAB5AFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUgBNAEYAMgBlAGwAZQBjAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADIAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAVwBoAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABJAG4AIABvAHIAZABlAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAbQBlAGcAYQB3AGEAdAB0ACAAaABvAHUAcgBzACAAdABvACAAawBpAGwAbwB3AGEAdAB0ACAAaABvAHUAcgBzACwAIAB0AGgAZQAgAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAAYQBuAGQAIABSAEUAQwBfAG8AbgBzAGkAdABlACAAdgBhAHIAaQBhAGIAbABlAHMAIABhAHIAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAGQAIABiAHkAIAAxADAAXgAzACAAaQBuAHMAdABlAGEAZAAgAG8AZgAgADEAMABeAC0AMwAuAFwAIgApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABhAHQAYQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -14177,23 +14208,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14210,4 +14225,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/14_Electricity_Scope2_WIP_v02.xlsx
+++ b/Excel/14_Electricity_Scope2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDA4AA0-669D-4B0D-BA79-CA098AA221D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244076A2-14A5-445D-9D14-FFCE063BD3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Input - Electricity" sheetId="70" r:id="rId5"/>
     <sheet name="14.1.1-2 Purchased electricity" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Electricity" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="126" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="127" r:id="rId8"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId9"/>
@@ -40,7 +40,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -56,9 +66,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -236,11 +265,19 @@
     <definedName name="Electricity_Equations.VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_LatexEquation">_xlfn.LAMBDA("E_{2,elec}=(Q_{elec} \times (1-(RPP+JRPP)) - ((REC_{surrendered}-REC_{onsite})\times 10^{3})) \times EF_{RMF2,elec} \times 10^{-3}")</definedName>
     <definedName name="Electricity_SourceData.Electricity_Scope2LocationBased_Description">_xlfn.LAMBDA(("Indirect (scope 2 and scope 3) location-based emission factors associated with the consumption and losses of purchased or acquired electricity"))</definedName>
     <definedName name="Electricity_SourceData.Electricity_Scope2MarketBased_Description">_xlfn.LAMBDA(("Table 2a Indirect (scope 2 and scope 3) emission factors from consumption of purchased or acquired electricity: market-based factors "))</definedName>
-    <definedName name="Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State, Territory or grid description","Scope 2 Emission Factors (kg CO2-e/kWh)","Scope 3 Emission Factors (kg CO2-e/kWh)";"New South Wales",0.64,0.03;"ACT",0.64,0.03;"Victoria",0.78,0.09;"Queensland",0.67,0.09;"South Australia",0.22,0.04;"Western Australia - South West Interconnected System (SWIS)",0.5,0.06;"Western Australia - North Western Interconnected System (NWIS)",0.56,0.09;"Tasmania",0.2,0.03;"Northern Territory - Darwin Katherine Interconnected System (DKIS)",0.56,0.09;"National",0.62,0.07}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(11, 3,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"State, Territory or grid description","Scope 2 Emission Factors (kg CO2-e/kWh)","Scope 3 Emission Factors (kg CO2-e/kWh)";"New South Wales",0.64,0.03;"ACT",0.64,0.03;"Victoria",0.78,0.09;"Queensland",0.67,0.09;"South Australia",0.22,0.04;"Western Australia - South West Interconnected System (SWIS)",0.5,0.06;"Western Australia - North Western Interconnected System (NWIS)",0.56,0.09;"Tasmania",0.2,0.03;"Northern Territory - Darwin Katherine Interconnected System (DKIS)",0.56,0.09;"National",0.62,0.07}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 1"))</definedName>
     <definedName name="Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Title">_xlfn.LAMBDA(("Electricity scope 2 and scope 3 location-based emission factors"))</definedName>
     <definedName name="Electricity_SourceData.Electricity_Scope2Scope3LocationBased_Variation">_xlfn.LAMBDA(("VARIATION OF SOURCE DATA: NSW and ACT split into separate rows."))</definedName>
-    <definedName name="Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State, Territory or grid description","Scope 2 Emission Factors (kg CO2-e/kWh)","Scope 2 Emission Factors (kg CO2-e/GJ)","Scope 3 Emission Factors (kg CO2 - e / kWh)","Scope 3 Emission Factors (kg CO2 - e / GJ)";"National",0.81,226,0.1,29}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(2, 5,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"State, Territory or grid description","Scope 2 Emission Factors (kg CO2-e/kWh)","Scope 2 Emission Factors (kg CO2-e/GJ)","Scope 3 Emission Factors (kg CO2 - e / kWh)","Scope 3 Emission Factors (kg CO2 - e / GJ)";"National",0.81,226,0.1,29}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 2a"))</definedName>
     <definedName name="Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Title">_xlfn.LAMBDA(("Electricity scope 2 and scope 3 market-based emission factors"))</definedName>
     <definedName name="Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Variation">_xlfn.LAMBDA((""))</definedName>
@@ -5549,16 +5586,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1C91172D-A190-4526-AF81-49F1D42FA3C6}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{7EC0241B-E0E6-479B-AF1A-B79DEAB80562}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{36E458F4-4187-4472-BCEB-8259ABB56D95}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{C84906BE-12AA-45F8-8F54-A03D7563BC3E}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1E9D048F-C654-4327-9D9E-81A9B913B4FE}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{5B84B522-E85A-4867-9342-B3ADE6D1C7B5}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5567,7 +5604,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3D4D21BD-7160-4BD1-BDC9-AA4D0C6E796B}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{21381986-276E-4754-B53D-701C4056BFE0}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5575,16 +5612,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DD96F4DC-FCCC-40BF-97CF-4B57609D1040}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{0679602C-B5B0-4D6A-BF39-46B784496384}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{262ADC43-FC39-4A25-AAF7-D481E9FA0633}" name="MAT">
+    <tableColumn id="2" xr3:uid="{C9BBA644-8218-4FFB-AC5F-08E51ACB75E1}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{755FDB7D-D062-4201-A414-EB162DDE34C2}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{222E007A-9EC4-4DFB-8702-B068E390AB01}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AB291061-0A75-4998-BCAD-AF06CFBF900E}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{5EE653A9-B929-4892-A2F8-AD78EC0D8C9B}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5593,7 +5630,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{9515D037-A997-4111-8200-B2CE963839E1}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{86CF939C-8894-4BC6-B572-98EFDFBA0DDC}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5601,16 +5638,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{538DE9A3-27B5-4162-961C-4DF76768A807}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{D3FA45B4-978B-49FF-BEFA-FB60DFBD8B9D}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AA0F4A4D-B90D-4532-B6B4-519286B6D5EA}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{3FC0659C-14C1-433C-835B-667811E7D069}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{55D08CC0-B7A7-4600-B121-C5790D8616D0}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{F9A42F6F-414B-4B26-A377-B093E45ED641}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{39EC0954-05EE-4353-A4AB-8602A371D94B}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{C7987428-A717-4599-955A-EDDDEAF0B426}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5619,16 +5656,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{F0E9FE68-57AA-4B53-B001-6DDBCD7A7879}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{62F9B600-2AD1-48B2-A429-DF44D926989C}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{12F71444-3408-4591-B72F-2319512461FA}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{BF3956A1-DC0F-4B24-9A8A-0838E0DDB883}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2A0D501C-ADE8-4FE5-AE61-F36450BE4683}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{64F2BA64-437B-4ADA-B51E-208E937213C3}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5637,16 +5674,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3D823E7A-0E7A-4D72-B430-F7C185190FF4}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{17729512-EA47-4D80-B0DD-1981BC35BA28}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C89C0117-D133-4F2D-81C2-94049D33B129}" name="Data source">
+    <tableColumn id="1" xr3:uid="{EF6473D8-3D3E-4850-B7D1-8CAB697443A7}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{27B7D1D5-DB8B-414F-BDAC-2EC7FABDDEE9}" name="Data score">
+    <tableColumn id="2" xr3:uid="{B6AF33B4-EB4C-4B38-ACC7-F1E556E1BA23}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5655,16 +5692,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{3DE7A940-A9C7-4DBE-81E2-39FBA5A0A31C}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{BE10B89F-9740-4469-900F-6D958F3FDD5B}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2B569132-4231-4B8D-BF98-593C48D39D92}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{94119A2D-E618-4CC4-8BCA-A91F3534D810}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B95425A4-B5DC-4C33-A446-028C6B30D1DB}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{5F55B0FD-C565-41BA-832D-9B919796DF94}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5673,7 +5710,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{1317C109-2EB7-4577-968C-965E5DA4773B}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B90B1B86-9D6E-499B-B654-FB51FC3D60BB}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5682,19 +5719,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D912E879-1BEE-4D12-BBED-A4AC1A965A5E}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{F8F1F99E-4734-43F9-9C24-505D44503124}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C186B542-E23F-4D37-935E-D2A54A169E5F}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{417C488C-A248-4871-9E97-8002B5890F5A}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6C010B63-3917-4052-BECE-44F6FC77D23F}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{7122A7E0-1544-4E78-B67B-E9C90C3E8670}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AA018E8B-CB7C-4242-8400-7B9C8365520D}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{694F23C1-148A-4BF8-B1B7-CF91CAB8F8BF}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{88B10D39-94B9-433A-B409-429FFD31DE9C}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{3661A926-D933-4E5B-9EEA-D007A23A6071}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5703,16 +5740,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{F442E8BA-BA2C-4E11-A1F1-E6B0087384DF}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{E3BB47E9-AA00-4B47-ACEE-8C4D43E11AC2}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4FFF1876-91BC-4BAB-9FBB-63E0CCEB55E0}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{BECBC629-FB73-4F42-A3D2-A7FF2D2872DA}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7C216B29-7E6F-4AB3-98EE-7C90F65C313F}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0BC2C2AA-C187-4975-AA0B-37CCCBDCD9EF}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5721,16 +5758,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{DFC4D39D-F4F0-4387-8981-56E2D578990D}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{8F4C4691-9695-4BA4-AD02-47D62194721A}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{325F428E-97D1-4236-9B8F-2900CECE4B32}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{9D25A25F-B9A3-4F27-A472-BB871801D4CA}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2179DE71-AFD0-4000-9BDE-481D62EAEFB1}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{EAA140B7-3F3B-4DC5-8866-12909BB8D6A8}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5739,16 +5776,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{37077460-6158-4309-AE1E-0A17D6C49270}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{F6F397D2-7A08-42D2-BF59-69C78F83EB50}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{42195ADF-B33E-43A2-AA19-1C520E4F2E62}" name="Month">
+    <tableColumn id="1" xr3:uid="{5D875851-F4FA-4306-8389-71E8AF5A7157}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D68D1EB5-6320-45AF-97CE-7027A3EC8A63}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F2E58981-11EE-47B8-8360-5EB3364BB58A}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5785,7 +5822,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{6F87E03A-C267-4420-9EDD-58F98BBA322F}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{90A01AB1-6B1F-4801-B521-0F8D2FFA949A}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5805,52 +5842,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{1C7087C7-B462-43D9-A7A1-4EAECE4EF690}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{9D657584-C878-4FEF-9389-893F848B79AE}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F8127CC-4664-4427-8B89-7D784FFAC935}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A2CC8BD1-6BED-4228-AB1C-0E0149C12E9E}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{81251917-8371-488F-9B02-6A8141CC2E05}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{17EEDE58-6C35-4413-B9B8-7E2FD1A780B1}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{79D84C04-2296-4E4F-AC89-675E82A48195}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{07A2EE0C-0688-480F-B3CF-6BF0ACB10E49}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D4EA1C5B-F74C-4A77-A4A9-779B718C8E32}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{3A493C66-336A-4B00-AD73-988D5730B638}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{665080C0-AAE6-4CC7-BD40-FB3899CF8CCB}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{3A8473C2-5C26-419F-BEA9-E4AA75BBC308}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{80CC931F-0E69-43D1-8612-1F3448C3660F}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{BE300641-2A80-4DDE-8180-3F33B774348C}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{469E6777-05FE-4211-A01B-967BAFC01452}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{A2B7D10B-FA57-4F40-BCF2-E1C4034B9F7C}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{647A4AAA-B1DD-47BB-B7A0-9A28F8A057CA}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{91AED598-7E4E-42EE-B608-6A4447EF7F92}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{90C66CEB-A9FB-4865-BDC8-D7786B07A8D3}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{478F2749-363F-4139-97A0-B019CEE01803}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2C8FB01D-DA3B-45BB-9F54-B6B382D53855}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{2B77A443-371C-43EB-B01C-0D72C3C08815}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EDC81F35-B339-46F6-8582-8BABE491E7D3}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{837E9FBF-3BFC-4B8C-9860-113E5284E4F3}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{DA72AC50-786C-4789-9830-9CB81B43FBF1}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{880E237C-9964-4622-9E6D-8772620C9FB0}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{8ADA3FCD-CE52-430C-8897-8B2F5379EBA5}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{716C76BA-3F3C-4F62-B9AE-16921A659AA0}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{5679F4BF-5B38-4C96-ACF2-E6AD5E082465}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{835B5EFC-B86F-436D-B446-122B2ACA9B1A}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{CB1C9779-B465-4B56-A215-28D214F650F1}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{F2A2BAA6-2758-4F01-B8F8-D7FDAE14E326}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5859,16 +5896,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{F0A1C1B7-6151-446F-BC07-E4CA929B278D}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{D2D55148-E230-4E6C-BF50-960EF410A603}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{097E74B0-21EF-4C6A-81C8-F36204B57AEA}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{3B21C23C-7B95-4245-93FA-1440841DA909}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{37BF67D8-D719-4D0B-A6AD-1E171A212315}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{53E09600-F07D-4704-824B-DF478974CB4B}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5929,20 +5966,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1E52A99D-2A16-47C5-B5DE-3E545EB57413}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E434A96A-68D0-4BF6-920D-08CEA46358E6}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{AC11A64C-3FBC-468E-B939-F5C855F173A4}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{90A94044-6919-44E4-915E-2073BFE656F3}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B4D0AE9E-DFA6-40F6-B60F-AAB5F1B9ED29}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{2A48FD95-A0C1-4BBA-A4F7-A5EA2638E497}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BE7DD25E-A7B6-4322-993F-5019FCBF1894}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{111B449A-9474-4A9A-BAC6-5E1C425671BF}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5951,12 +5988,12 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{84D8F464-425B-4CFB-8157-CE34DB6DC5F7}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9E69F68B-227D-4F1D-B80D-950C18C55C77}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{39194284-C283-4B1E-B27D-939A14C3665F}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{BE0118F8-5B51-445C-ACC6-BAEBDB18F98B}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5965,16 +6002,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1AA18832-A6CE-4390-AD94-78D0BC0D2ECE}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{8A6436B2-59FD-499C-8042-F4B5DCFBA6FB}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{98057B67-9734-4328-9236-810DFB4D1014}" name="Gas">
+    <tableColumn id="1" xr3:uid="{5D769CCE-BC8F-4DEB-82D7-C8E02303B066}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0D614BB9-6CA3-49C5-9DE9-711083A17F56}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{CDEE4027-FC80-4DCA-B857-0B090859239D}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5983,7 +6020,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4C084481-A30B-47C6-BA75-0A7C8BB676FB}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{CDBFE1E9-16BB-4CB2-A502-A8F1ACED0BBA}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5992,19 +6029,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7D58DF5F-8927-46FF-981D-879830A90573}" name="Gas">
+    <tableColumn id="1" xr3:uid="{22F62220-CAAC-4357-A8F3-D4F8CE2A41F0}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{02709203-EF59-4CA0-941E-A974D34C1026}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{F361C48E-71B9-4614-B50B-BBD8F2E67099}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{594CF733-99E0-4CB7-A410-882637753ED1}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{7D11F575-4D1D-4C24-AF34-A118761114B3}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5E193D03-9BE6-4BE9-A59E-0EBC8657E396}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{176EF279-16D1-486B-8197-F373E1ACB551}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{083F510C-6261-4211-86E1-A01986E873C6}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{FF15131F-5E18-4892-B392-2BEFAA301670}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6013,7 +6050,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D5DC7FE5-F74F-4D8E-AA1E-C71AA8CFEE7F}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{9621B593-EB01-4D4F-BCA1-A445061506D4}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6033,52 +6070,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{6BA3AD44-ACBE-4644-A92F-5FC71FC237EA}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{1FE190DC-0653-4D09-93D7-011296A69A6A}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{72F1645A-787D-4145-9FC3-BF4411E19E07}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{0D19CC47-418F-4FB3-9A24-6B72F428D11A}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E9ABD992-0246-4394-9BF8-1E49E3AE3C0F}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{8D8EAAF3-2329-4DF2-B357-8048FACE8638}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F171E21B-CC7B-4E49-AC46-757DC8B21A35}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{97B85569-6C24-4C48-B5E6-F4591C1F959B}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E7D65B18-7D7B-4118-BEF8-93088B8CBF85}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{E953E51B-D4A8-442C-B776-17D46705AB2C}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{CDFD0BAB-9E03-4B36-B23A-88A5242452D6}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{AF9B3876-60D5-4B75-8CD3-CDB9191487B4}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{0E1CFFF6-3DB6-4AC5-9C74-9F9D223502CF}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{BFF65DC8-6883-4DB3-AF35-A1E18D24CD83}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6F12C6E7-8816-41A2-937F-F82FFCDB9446}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{9B3A1F25-7141-45E3-B71F-B9842C539696}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{966E2354-F061-464E-BC29-988BE9BEA0A9}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{15D17611-1328-41D2-9170-AC031E9C9970}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{DE8304D5-7AC5-49AD-9CF5-0122B9813D35}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{E74802D7-01A2-447F-849A-52AADCEF1F15}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{396701DB-621F-41F5-8581-149AF540D3E0}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{30485F87-BAF9-410B-8F38-5B1277CF1023}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{FC278AD2-9E30-41DB-83B1-14F92C3BA27C}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{101D4F94-78C8-47F7-AD1F-33246B9A08DE}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{37B3BDA5-B646-43FB-ADA6-A99DA90CC892}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{1F7C2EBD-A37C-4E66-9DD2-4AA5CF953BCE}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{6DAFF6E8-C962-4332-B4B8-1F011653A00D}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{C5168F5D-E649-4D23-A6FA-01FDC5E721CE}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B7332DDD-FAC4-4C56-A188-03FAA81B2BA5}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{E251B643-8AD9-4FF9-8608-C89F6CBDE7F5}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{5A9ABF7F-9E59-46B2-A502-FCBB6598DDCB}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{3BAC8FF1-7205-4F44-A1E8-6F4181415306}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9979,7 +10016,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4049A772-9457-4A76-B2C2-E44B01198C50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00042409-3434-4780-840C-6BA07F554401}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Excel/14_Electricity_Scope2_WIP_v02.xlsx
+++ b/Excel/14_Electricity_Scope2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5B9E96-D379-4354-BE6F-01B593AD85B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7118987-7BC6-478D-ADE8-2C4CB97C06BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -7560,7 +7560,7 @@
         <v>103</v>
       </c>
       <c r="E13" s="75">
-        <f>DATE(YEAR(E12)+1,MONTH(E12),DAY(E12))-1</f>
+        <f>DATE(YEAR(X_Cell_Site_StartDate)+1,MONTH(X_Cell_Site_StartDate),DAY(X_Cell_Site_StartDate))-1</f>
         <v>45657</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -8600,7 +8600,7 @@
         <v>141</v>
       </c>
       <c r="E29" s="112" t="str">
-        <f>TEXT('Input - Site'!E12, "dd mmm yyyy")</f>
+        <f>TEXT(X_Cell_Site_StartDate, "dd mmm yyyy")</f>
         <v>01 Jan 2024</v>
       </c>
       <c r="K29" s="47"/>
@@ -8610,7 +8610,7 @@
         <v>126</v>
       </c>
       <c r="E30" s="112" t="str">
-        <f>TEXT('Input - Site'!E13, "dd mmm yyyy")</f>
+        <f>TEXT(X_Cell_Site_EndDate, "dd mmm yyyy")</f>
         <v>31 Dec 2024</v>
       </c>
       <c r="K30" s="47"/>
@@ -9184,8 +9184,8 @@
       <c r="D8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E8" ca="1">Common_InputFunctions.Utility_DisplayFunctionName(E18)</f>
+      <c r="E8" s="11" t="str">
+        <f ca="1">Common_InputFunctions.Utility_DisplayFunctionName(VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1)</f>
         <v>=Electricity_Equations.VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions</v>
       </c>
     </row>
@@ -9352,8 +9352,8 @@
       <c r="D25" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E25" ca="1">Common_InputFunctions.Utility_DisplayFunctionName(E39)</f>
+      <c r="E25" s="11" t="str">
+        <f ca="1">Common_InputFunctions.Utility_DisplayFunctionName(VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1)</f>
         <v>=Electricity_Equations.VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation</v>
       </c>
     </row>
@@ -14453,14 +14453,7 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBJAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADIAIABhAG4AZAAgAHMAYwBvAHAAZQAgADMAKQAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABhAHMAcwBvAGMAaQBhAHQAZQBkACAAdwBpAHQAaAAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQBuAGQAIABsAG8AcwBzAGUAcwAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbwByACAAYQBjAHEAdQBpAHIAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAsACAAVABlAHIAcgBpAHQAbwByAHkAIABvAHIAIABnAHIAaQBkACAAZABlAHMAYwByAGkAcAB0AGkAbwBuAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADIAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAtAGUALwBrAFcAaAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAtAGUALwBrAFcAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMAAuADYANAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADYANAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADAALgA3ADgALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAMAAuADYANwAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAMAAuADIAMgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0ACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAFMAVwBJAFMAKQBcACIALAAgADAALgA1ADAALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABlAHIAbgAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABOAFcASQBTACkAXAAiACwAIAAwAC4ANQA2ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAMAAuADIAMAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAALQAgAEQAYQByAHcAaQBuACAASwBhAHQAaABlAHIAaQBuAGUAIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgARABLAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AGkAbwBuAGEAbABcACIALAAgADAALgA2ADIALAAgADAALgAwADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFIAZQBzAGkAZAB1AGEAbAAgAE0AaQB4ACAARgBhAGMAdABvAHIAIABmAG8AcgAgAG0AYQByAGsAZQB0AC0AYgBhAHMAZQBkACAAZQBxAHUAYQB0AGkAbwBuAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHMAYwBvAHAAZQAgADIAIABhAG4AZAAgAHMAYwBvAHAAZQAgADMAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAAMgBhACAASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgByAG8AbQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbwByACAAYQBjAHEAdQBpAHIAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ADoAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGYAYQBjAHQAbwByAHMAIABcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAMgBhAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAAawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4AOAAxACwAIAAyADIANgAsACAAMAAuADEAMAAsACAAMgA5AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADQAOgAgAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA0AC4AMQAuADEAIABQAHUAcgBjAGgAYQBzAGUAZAAgAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgACgATABvAGMAYQB0AGkAbwBuAC0AQgBhAHMAZQBkACkAXABuADEANAAuADEALgAyACAAUAB1AHIAYwBoAGEAcwBlAGQAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAE0AYQByAGsAZQB0AC0AQgBhAHMAZQBkACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAF8AMgBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMgAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZAAgACgAawBXAGgAKQBcAG4ARQBGAF8AMgBlAGwAZQBjACAAPQAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABrAGcAIABDAE8AMgBlAC8AawBXAGgAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZQBsAGUAYwAsACAARQBGAF8AMgBlAGwAZQBjACwAXABuACAAIAAgACAAUQBfAGUAbABlAGMAIAAqACAARQBGAF8AMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADIAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAyACwAZQBsAGUAYwB9AD0AUQBfAHsAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7ADIALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AMgBlAGwAZQBjAFwAIgAsACAAXAAiAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGUAZAAgAGcAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABjAGEAcAB0AHUAcgBlACAAdwBoAGkAYwBoACAAZwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAEUAXwAyAGUAbABlAGMAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewAyACwAZQBsAGUAYwB9AD0AKAAoAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAKQApAC0AKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkACAAKABrAFcAaAApAFwAbgBSAFAAUAAgAD0AIABSAGUAbgBlAHcAYQBiAGwAZQAgAFAAbwB3AGUAcgAgAFAAZQByAGMAZQBuAHQAYQBnAGUAIAB1AG4AZABlAHIAIAB0AGgAZQAgAEwAYQByAGcAZQAtAHMAYwBhAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABUAGEAcgBnAGUAdAAgACgATABSAEUAVAApACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZAAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAEoAUgBQAFAAIAA9ACAAagB1AHIAaQBzAGQAaQBjAHQAaQBvAG4AYQBsACAAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZAAgACgAbwBuAGwAeQAgAGEAcABwAGwAaQBlAHMAIAB0AG8AIAB0AGgAZQAgAEEAQwBUACkAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGUAbABpAGcAaQBiAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHAAbwByAHQAaQBuAGcAIAB5AGUAYQByACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgACgATQBXAGgAKQBcAG4AUgBFAEMAXwBvAG4AcwBpAHQAZQAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGUAbABpAGcAaQBiAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHQAaABhAHQAIABoAGEAdgBlACAAYgBlAGUAbgAgAG8AcgAgAHcAaQBsAGwAIABiAGUAIABpAHMAcwB1AGUAZAAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAByAG8AZAB1AGMAZQBkACAAbwBuAC0AcwBpAHQAZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIAB5AGUAYQByACAAYQBuAGQAIABjAG8AbgBzAHUAbQBlAGQAIABiAHkAIAB0AGgAZQAgAGUAbgB0AGkAdAB5ACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgACgATQBXAGgAKQBcAG4ARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAPQAgAFMAYwBvAHAAZQAgADIAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAGsAZwAgAEMATwAyAGUALwBrAFcAaAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAALQAzACkAKQAgACoAIABFAEYAXwBSAE0ARgAyAGUAbABlAGMAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAAMwApACkAIAAqACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADIAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANAAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADIALABlAGwAZQBjAH0APQAoAFEAXwB7AGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAIAAtACAAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQApACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMgAsAGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMgAsAGUAbABlAGMAfQA9ACgAUQBfAHsAZQBsAGUAYwB9ACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAKQAgAC0AIAAoACgAUgBFAEMAXwB7AHMAdQByAHIAZQBuAGQAZQByAGUAZAB9AC0AUgBFAEMAXwB7AG8AbgBzAGkAdABlAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AKQApACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMgAsAGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBQAFAAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABQAG8AdwBlAHIAIABQAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAAdABoAGUAIABMAGEAcgBnAGUALQBzAGMAYQBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAVABhAHIAZwBlAHQAIAAoAEwAUgBFAFQAKQBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAFIAUABQAFwAIgAsACAAXAAiAGoAdQByAGkAcwBkAGkAYwB0AGkAbwBuAGEAbAAgAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAEEAQwBUACAAbwBuAGwAeQApAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHAAbwByAHQAaQBuAGcAIAB5AGUAYQByAFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBFAEMAXwBvAG4AcwBpAHQAZQBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIABpAHMAcwB1AGUAZAAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAByAG8AZAB1AGMAZQBkACAAbwBuAC0AcwBpAHQAZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIAB5AGUAYQByACAAYQBuAGQAIABjAG8AbgBzAHUAbQBlAGQAIABiAHkAIAB0AGgAZQAgAGUAbgB0AGkAdAB5AFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUgBNAEYAMgBlAGwAZQBjAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADIAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAVwBoAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABJAG4AIABvAHIAZABlAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAbQBlAGcAYQB3AGEAdAB0ACAAaABvAHUAcgBzACAAdABvACAAawBpAGwAbwB3AGEAdAB0ACAAaABvAHUAcgBzACwAIAB0AGgAZQAgAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAAYQBuAGQAIABSAEUAQwBfAG8AbgBzAGkAdABlACAAdgBhAHIAaQBhAGIAbABlAHMAIABhAHIAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAGQAIABiAHkAIAAxADAAXgAzACAAaQBuAHMAdABlAGEAZAAgAG8AZgAgADEAMABeAC0AMwAuAFwAIgApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABhAHQAYQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14659,7 +14652,14 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBJAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADIAIABhAG4AZAAgAHMAYwBvAHAAZQAgADMAKQAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABhAHMAcwBvAGMAaQBhAHQAZQBkACAAdwBpAHQAaAAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQBuAGQAIABsAG8AcwBzAGUAcwAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbwByACAAYQBjAHEAdQBpAHIAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAsACAAVABlAHIAcgBpAHQAbwByAHkAIABvAHIAIABnAHIAaQBkACAAZABlAHMAYwByAGkAcAB0AGkAbwBuAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADIAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAtAGUALwBrAFcAaAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAtAGUALwBrAFcAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMAAuADYANAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADYANAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADAALgA3ADgALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAMAAuADYANwAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAMAAuADIAMgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0ACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAFMAVwBJAFMAKQBcACIALAAgADAALgA1ADAALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABlAHIAbgAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABOAFcASQBTACkAXAAiACwAIAAwAC4ANQA2ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAMAAuADIAMAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAALQAgAEQAYQByAHcAaQBuACAASwBhAHQAaABlAHIAaQBuAGUAIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgARABLAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AGkAbwBuAGEAbABcACIALAAgADAALgA2ADIALAAgADAALgAwADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFIAZQBzAGkAZAB1AGEAbAAgAE0AaQB4ACAARgBhAGMAdABvAHIAIABmAG8AcgAgAG0AYQByAGsAZQB0AC0AYgBhAHMAZQBkACAAZQBxAHUAYQB0AGkAbwBuAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHMAYwBvAHAAZQAgADIAIABhAG4AZAAgAHMAYwBvAHAAZQAgADMAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAAMgBhACAASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgByAG8AbQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbwByACAAYQBjAHEAdQBpAHIAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ADoAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGYAYQBjAHQAbwByAHMAIABcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAMgBhAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAAawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4AOAAxACwAIAAyADIANgAsACAAMAAuADEAMAAsACAAMgA5AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADQAOgAgAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA0AC4AMQAuADEAIABQAHUAcgBjAGgAYQBzAGUAZAAgAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgACgATABvAGMAYQB0AGkAbwBuAC0AQgBhAHMAZQBkACkAXABuADEANAAuADEALgAyACAAUAB1AHIAYwBoAGEAcwBlAGQAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAE0AYQByAGsAZQB0AC0AQgBhAHMAZQBkACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAF8AMgBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMgAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZAAgACgAawBXAGgAKQBcAG4ARQBGAF8AMgBlAGwAZQBjACAAPQAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABrAGcAIABDAE8AMgBlAC8AawBXAGgAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZQBsAGUAYwAsACAARQBGAF8AMgBlAGwAZQBjACwAXABuACAAIAAgACAAUQBfAGUAbABlAGMAIAAqACAARQBGAF8AMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADIAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAyACwAZQBsAGUAYwB9AD0AUQBfAHsAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7ADIALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AMgBlAGwAZQBjAFwAIgAsACAAXAAiAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGUAZAAgAGcAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABjAGEAcAB0AHUAcgBlACAAdwBoAGkAYwBoACAAZwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAEUAXwAyAGUAbABlAGMAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewAyACwAZQBsAGUAYwB9AD0AKAAoAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAKQApAC0AKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkACAAKABrAFcAaAApAFwAbgBSAFAAUAAgAD0AIABSAGUAbgBlAHcAYQBiAGwAZQAgAFAAbwB3AGUAcgAgAFAAZQByAGMAZQBuAHQAYQBnAGUAIAB1AG4AZABlAHIAIAB0AGgAZQAgAEwAYQByAGcAZQAtAHMAYwBhAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABUAGEAcgBnAGUAdAAgACgATABSAEUAVAApACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZAAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAEoAUgBQAFAAIAA9ACAAagB1AHIAaQBzAGQAaQBjAHQAaQBvAG4AYQBsACAAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZAAgACgAbwBuAGwAeQAgAGEAcABwAGwAaQBlAHMAIAB0AG8AIAB0AGgAZQAgAEEAQwBUACkAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGUAbABpAGcAaQBiAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHAAbwByAHQAaQBuAGcAIAB5AGUAYQByACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgACgATQBXAGgAKQBcAG4AUgBFAEMAXwBvAG4AcwBpAHQAZQAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGUAbABpAGcAaQBiAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHQAaABhAHQAIABoAGEAdgBlACAAYgBlAGUAbgAgAG8AcgAgAHcAaQBsAGwAIABiAGUAIABpAHMAcwB1AGUAZAAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAByAG8AZAB1AGMAZQBkACAAbwBuAC0AcwBpAHQAZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIAB5AGUAYQByACAAYQBuAGQAIABjAG8AbgBzAHUAbQBlAGQAIABiAHkAIAB0AGgAZQAgAGUAbgB0AGkAdAB5ACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgACgATQBXAGgAKQBcAG4ARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAPQAgAFMAYwBvAHAAZQAgADIAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAGsAZwAgAEMATwAyAGUALwBrAFcAaAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAALQAzACkAKQAgACoAIABFAEYAXwBSAE0ARgAyAGUAbABlAGMAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAAMwApACkAIAAqACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADIAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANAAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADIALABlAGwAZQBjAH0APQAoAFEAXwB7AGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAIAAtACAAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQApACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMgAsAGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMgAsAGUAbABlAGMAfQA9ACgAUQBfAHsAZQBsAGUAYwB9ACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAKQAgAC0AIAAoACgAUgBFAEMAXwB7AHMAdQByAHIAZQBuAGQAZQByAGUAZAB9AC0AUgBFAEMAXwB7AG8AbgBzAGkAdABlAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AKQApACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMgAsAGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBQAFAAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABQAG8AdwBlAHIAIABQAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAAdABoAGUAIABMAGEAcgBnAGUALQBzAGMAYQBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAVABhAHIAZwBlAHQAIAAoAEwAUgBFAFQAKQBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAFIAUABQAFwAIgAsACAAXAAiAGoAdQByAGkAcwBkAGkAYwB0AGkAbwBuAGEAbAAgAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAEEAQwBUACAAbwBuAGwAeQApAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHAAbwByAHQAaQBuAGcAIAB5AGUAYQByAFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBFAEMAXwBvAG4AcwBpAHQAZQBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIABpAHMAcwB1AGUAZAAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAByAG8AZAB1AGMAZQBkACAAbwBuAC0AcwBpAHQAZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIAB5AGUAYQByACAAYQBuAGQAIABjAG8AbgBzAHUAbQBlAGQAIABiAHkAIAB0AGgAZQAgAGUAbgB0AGkAdAB5AFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUgBNAEYAMgBlAGwAZQBjAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADIAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAVwBoAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABJAG4AIABvAHIAZABlAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAbQBlAGcAYQB3AGEAdAB0ACAAaABvAHUAcgBzACAAdABvACAAawBpAGwAbwB3AGEAdAB0ACAAaABvAHUAcgBzACwAIAB0AGgAZQAgAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAAYQBuAGQAIABSAEUAQwBfAG8AbgBzAGkAdABlACAAdgBhAHIAaQBhAGIAbABlAHMAIABhAHIAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAGQAIABiAHkAIAAxADAAXgAzACAAaQBuAHMAdABlAGEAZAAgAG8AZgAgADEAMABeAC0AMwAuAFwAIgApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABhAHQAYQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14671,12 +14671,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14701,9 +14698,12 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/14_Electricity_Scope2_WIP_v02.xlsx
+++ b/Excel/14_Electricity_Scope2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7118987-7BC6-478D-ADE8-2C4CB97C06BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E56E0D1-1A4A-487C-8B6F-2201D91CAD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2145" yWindow="2460" windowWidth="36255" windowHeight="19140" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -281,23 +281,6 @@
     <definedName name="Fertiliser_Equations_Lime.VEERG_5_3_1_1__1_LimeApplication">_xlfn.LAMBDA(_xlpm.Mlime,_xlpm.FracLime,_xlpm.Plime,_xlpm.EFlime,_xlpm.FracDol,_xlpm.Pdol,_xlpm.EFdol,_xlpm.CgCO2, ((_xlpm.Mlime * _xlpm.FracLime * _xlpm.Plime * _xlpm.EFlime) + (_xlpm.Mlime * _xlpm.FracDol * _xlpm.Pdol * _xlpm.EFdol)) * _xlpm.CgCO2 * 10 ^ -3)</definedName>
     <definedName name="Fertiliser_Equations_Organic.VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser">_xlfn.LAMBDA(_xlpm.Morganicjf,_xlpm.FNorganicf, _xlpm.Morganicjf * _xlpm.FNorganicf)</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
-    <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
-    <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_CO2_for_carbonation">#REF!</definedName>
-    <definedName name="Input_Cell_CO2forcarbonation">#REF!</definedName>
-    <definedName name="Input_Cell_Livestock_antibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_Livestock_tags">#REF!</definedName>
-    <definedName name="Input_Cell_LivestockAntibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_Nylon_netting_for_horticulture">#REF!</definedName>
-    <definedName name="Input_Cell_Nylonnettingforhorticulture">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets__Plastic">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
-    <definedName name="Range_LivestockStartingValues">#REF!</definedName>
-    <definedName name="Step1">#REF!</definedName>
-    <definedName name="Step2">#REF!</definedName>
-    <definedName name="Step3">#REF!</definedName>
     <definedName name="VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1">'14.1.1-2 Purchased electricity'!$E$18</definedName>
     <definedName name="VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1">'14.1.1-2 Purchased electricity'!$E$39</definedName>
     <definedName name="X_Cell_Electricity_CalculationMethod">'Input - Electricity'!$E$5</definedName>
@@ -14444,19 +14427,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBJAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADIAIABhAG4AZAAgAHMAYwBvAHAAZQAgADMAKQAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABhAHMAcwBvAGMAaQBhAHQAZQBkACAAdwBpAHQAaAAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQBuAGQAIABsAG8AcwBzAGUAcwAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbwByACAAYQBjAHEAdQBpAHIAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAsACAAVABlAHIAcgBpAHQAbwByAHkAIABvAHIAIABnAHIAaQBkACAAZABlAHMAYwByAGkAcAB0AGkAbwBuAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADIAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAtAGUALwBrAFcAaAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAtAGUALwBrAFcAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMAAuADYANAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADYANAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADAALgA3ADgALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAMAAuADYANwAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAMAAuADIAMgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0ACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAFMAVwBJAFMAKQBcACIALAAgADAALgA1ADAALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABlAHIAbgAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABOAFcASQBTACkAXAAiACwAIAAwAC4ANQA2ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAMAAuADIAMAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAALQAgAEQAYQByAHcAaQBuACAASwBhAHQAaABlAHIAaQBuAGUAIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgARABLAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AGkAbwBuAGEAbABcACIALAAgADAALgA2ADIALAAgADAALgAwADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFIAZQBzAGkAZAB1AGEAbAAgAE0AaQB4ACAARgBhAGMAdABvAHIAIABmAG8AcgAgAG0AYQByAGsAZQB0AC0AYgBhAHMAZQBkACAAZQBxAHUAYQB0AGkAbwBuAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHMAYwBvAHAAZQAgADIAIABhAG4AZAAgAHMAYwBvAHAAZQAgADMAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAAMgBhACAASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgByAG8AbQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbwByACAAYQBjAHEAdQBpAHIAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ADoAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGYAYQBjAHQAbwByAHMAIABcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAMgBhAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAAawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4AOAAxACwAIAAyADIANgAsACAAMAAuADEAMAAsACAAMgA5AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADQAOgAgAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA0AC4AMQAuADEAIABQAHUAcgBjAGgAYQBzAGUAZAAgAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgACgATABvAGMAYQB0AGkAbwBuAC0AQgBhAHMAZQBkACkAXABuADEANAAuADEALgAyACAAUAB1AHIAYwBoAGEAcwBlAGQAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAE0AYQByAGsAZQB0AC0AQgBhAHMAZQBkACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAF8AMgBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMgAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZAAgACgAawBXAGgAKQBcAG4ARQBGAF8AMgBlAGwAZQBjACAAPQAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABrAGcAIABDAE8AMgBlAC8AawBXAGgAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZQBsAGUAYwAsACAARQBGAF8AMgBlAGwAZQBjACwAXABuACAAIAAgACAAUQBfAGUAbABlAGMAIAAqACAARQBGAF8AMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADIAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAyACwAZQBsAGUAYwB9AD0AUQBfAHsAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7ADIALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AMgBlAGwAZQBjAFwAIgAsACAAXAAiAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGUAZAAgAGcAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABjAGEAcAB0AHUAcgBlACAAdwBoAGkAYwBoACAAZwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAEUAXwAyAGUAbABlAGMAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewAyACwAZQBsAGUAYwB9AD0AKAAoAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAKQApAC0AKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkACAAKABrAFcAaAApAFwAbgBSAFAAUAAgAD0AIABSAGUAbgBlAHcAYQBiAGwAZQAgAFAAbwB3AGUAcgAgAFAAZQByAGMAZQBuAHQAYQBnAGUAIAB1AG4AZABlAHIAIAB0AGgAZQAgAEwAYQByAGcAZQAtAHMAYwBhAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABUAGEAcgBnAGUAdAAgACgATABSAEUAVAApACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZAAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAEoAUgBQAFAAIAA9ACAAagB1AHIAaQBzAGQAaQBjAHQAaQBvAG4AYQBsACAAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZAAgACgAbwBuAGwAeQAgAGEAcABwAGwAaQBlAHMAIAB0AG8AIAB0AGgAZQAgAEEAQwBUACkAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGUAbABpAGcAaQBiAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHAAbwByAHQAaQBuAGcAIAB5AGUAYQByACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgACgATQBXAGgAKQBcAG4AUgBFAEMAXwBvAG4AcwBpAHQAZQAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGUAbABpAGcAaQBiAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHQAaABhAHQAIABoAGEAdgBlACAAYgBlAGUAbgAgAG8AcgAgAHcAaQBsAGwAIABiAGUAIABpAHMAcwB1AGUAZAAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAByAG8AZAB1AGMAZQBkACAAbwBuAC0AcwBpAHQAZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIAB5AGUAYQByACAAYQBuAGQAIABjAG8AbgBzAHUAbQBlAGQAIABiAHkAIAB0AGgAZQAgAGUAbgB0AGkAdAB5ACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgACgATQBXAGgAKQBcAG4ARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAPQAgAFMAYwBvAHAAZQAgADIAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAGsAZwAgAEMATwAyAGUALwBrAFcAaAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAALQAzACkAKQAgACoAIABFAEYAXwBSAE0ARgAyAGUAbABlAGMAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAAMwApACkAIAAqACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADIAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANAAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADIALABlAGwAZQBjAH0APQAoAFEAXwB7AGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAIAAtACAAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQApACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMgAsAGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMgAsAGUAbABlAGMAfQA9ACgAUQBfAHsAZQBsAGUAYwB9ACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAKQAgAC0AIAAoACgAUgBFAEMAXwB7AHMAdQByAHIAZQBuAGQAZQByAGUAZAB9AC0AUgBFAEMAXwB7AG8AbgBzAGkAdABlAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AKQApACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMgAsAGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBQAFAAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABQAG8AdwBlAHIAIABQAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAAdABoAGUAIABMAGEAcgBnAGUALQBzAGMAYQBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAVABhAHIAZwBlAHQAIAAoAEwAUgBFAFQAKQBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAFIAUABQAFwAIgAsACAAXAAiAGoAdQByAGkAcwBkAGkAYwB0AGkAbwBuAGEAbAAgAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAEEAQwBUACAAbwBuAGwAeQApAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHAAbwByAHQAaQBuAGcAIAB5AGUAYQByAFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBFAEMAXwBvAG4AcwBpAHQAZQBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIABpAHMAcwB1AGUAZAAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAByAG8AZAB1AGMAZQBkACAAbwBuAC0AcwBpAHQAZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIAB5AGUAYQByACAAYQBuAGQAIABjAG8AbgBzAHUAbQBlAGQAIABiAHkAIAB0AGgAZQAgAGUAbgB0AGkAdAB5AFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUgBNAEYAMgBlAGwAZQBjAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADIAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAVwBoAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABJAG4AIABvAHIAZABlAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAbQBlAGcAYQB3AGEAdAB0ACAAaABvAHUAcgBzACAAdABvACAAawBpAGwAbwB3AGEAdAB0ACAAaABvAHUAcgBzACwAIAB0AGgAZQAgAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAAYQBuAGQAIABSAEUAQwBfAG8AbgBzAGkAdABlACAAdgBhAHIAaQBhAGIAbABlAHMAIABhAHIAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAGQAIABiAHkAIAAxADAAXgAzACAAaQBuAHMAdABlAGEAZAAgAG8AZgAgADEAMABeAC0AMwAuAFwAIgApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABhAHQAYQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -14651,6 +14621,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBJAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADIAIABhAG4AZAAgAHMAYwBvAHAAZQAgADMAKQAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABhAHMAcwBvAGMAaQBhAHQAZQBkACAAdwBpAHQAaAAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQBuAGQAIABsAG8AcwBzAGUAcwAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbwByACAAYQBjAHEAdQBpAHIAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADEAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAsACAAVABlAHIAcgBpAHQAbwByAHkAIABvAHIAIABnAHIAaQBkACAAZABlAHMAYwByAGkAcAB0AGkAbwBuAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADIAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAtAGUALwBrAFcAaAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAKABrAGcAIABDAE8AMgAtAGUALwBrAFcAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMAAuADYANAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADYANAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADAALgA3ADgALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAMAAuADYANwAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAMAAuADIAMgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0ACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAFMAVwBJAFMAKQBcACIALAAgADAALgA1ADAALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABlAHIAbgAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABOAFcASQBTACkAXAAiACwAIAAwAC4ANQA2ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAMAAuADIAMAAsACAAMAAuADAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAALQAgAEQAYQByAHcAaQBuACAASwBhAHQAaABlAHIAaQBuAGUAIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgARABLAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AGkAbwBuAGEAbABcACIALAAgADAALgA2ADIALAAgADAALgAwADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFIAZQBzAGkAZAB1AGEAbAAgAE0AaQB4ACAARgBhAGMAdABvAHIAIABmAG8AcgAgAG0AYQByAGsAZQB0AC0AYgBhAHMAZQBkACAAZQBxAHUAYQB0AGkAbwBuAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHMAYwBvAHAAZQAgADIAIABhAG4AZAAgAHMAYwBvAHAAZQAgADMAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAAMgBhACAASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgByAG8AbQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbwByACAAYQBjAHEAdQBpAHIAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ADoAIABtAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAGYAYQBjAHQAbwByAHMAIABcACIAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAMgBhAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAAawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4AOAAxACwAIAAyADIANgAsACAAMAAuADEAMAAsACAAMgA5AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADQAOgAgAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA0AC4AMQAuADEAIABQAHUAcgBjAGgAYQBzAGUAZAAgAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgACgATABvAGMAYQB0AGkAbwBuAC0AQgBhAHMAZQBkACkAXABuADEANAAuADEALgAyACAAUAB1AHIAYwBoAGEAcwBlAGQAIABFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAE0AYQByAGsAZQB0AC0AQgBhAHMAZQBkACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAF8AMgBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMgAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAyACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZAAgACgAawBXAGgAKQBcAG4ARQBGAF8AMgBlAGwAZQBjACAAPQAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAKABrAGcAIABDAE8AMgBlAC8AawBXAGgAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZQBsAGUAYwAsACAARQBGAF8AMgBlAGwAZQBjACwAXABuACAAIAAgACAAUQBfAGUAbABlAGMAIAAqACAARQBGAF8AMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAUwBjAG8AcABlACAAMgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADIAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAyACwAZQBsAGUAYwB9AD0AUQBfAHsAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7ADIALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AMgBlAGwAZQBjAFwAIgAsACAAXAAiAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGUAZAAgAGcAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABjAGEAcAB0AHUAcgBlACAAdwBoAGkAYwBoACAAZwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4ATQBhAHIAawBlAHQALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAEUAXwAyAGUAbABlAGMAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewAyACwAZQBsAGUAYwB9AD0AKAAoAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAKQApAC0AKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADIALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkACAAKABrAFcAaAApAFwAbgBSAFAAUAAgAD0AIABSAGUAbgBlAHcAYQBiAGwAZQAgAFAAbwB3AGUAcgAgAFAAZQByAGMAZQBuAHQAYQBnAGUAIAB1AG4AZABlAHIAIAB0AGgAZQAgAEwAYQByAGcAZQAtAHMAYwBhAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABUAGEAcgBnAGUAdAAgACgATABSAEUAVAApACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZAAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAEoAUgBQAFAAIAA9ACAAagB1AHIAaQBzAGQAaQBjAHQAaQBvAG4AYQBsACAAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZAAgACgAbwBuAGwAeQAgAGEAcABwAGwAaQBlAHMAIAB0AG8AIAB0AGgAZQAgAEEAQwBUACkAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGUAbABpAGcAaQBiAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHAAbwByAHQAaQBuAGcAIAB5AGUAYQByACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgACgATQBXAGgAKQBcAG4AUgBFAEMAXwBvAG4AcwBpAHQAZQAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGUAbABpAGcAaQBiAGwAZQAgAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHQAaABhAHQAIABoAGEAdgBlACAAYgBlAGUAbgAgAG8AcgAgAHcAaQBsAGwAIABiAGUAIABpAHMAcwB1AGUAZAAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAByAG8AZAB1AGMAZQBkACAAbwBuAC0AcwBpAHQAZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIAB5AGUAYQByACAAYQBuAGQAIABjAG8AbgBzAHUAbQBlAGQAIABiAHkAIAB0AGgAZQAgAGUAbgB0AGkAdAB5ACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAHQAbwAgAG0AZQBnAGEAdwBhAHQAdAAgAGgAbwB1AHIAcwAgACgATQBXAGgAKQBcAG4ARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAPQAgAFMAYwBvAHAAZQAgADIAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAoAGsAZwAgAEMATwAyAGUALwBrAFcAaAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAALQAzACkAKQAgACoAIABFAEYAXwBSAE0ARgAyAGUAbABlAGMAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAAMwApACkAIAAqACAARQBGAF8AUgBNAEYAMgBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcgBrAGUAdAAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADIAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANAAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADIALABlAGwAZQBjAH0APQAoAFEAXwB7AGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAoADEALQAoAFIAUABQACsASgBSAFAAUAApACkAIAAtACAAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQApACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMgAsAGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMgAsAGUAbABlAGMAfQA9ACgAUQBfAHsAZQBsAGUAYwB9ACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAKQAgAC0AIAAoACgAUgBFAEMAXwB7AHMAdQByAHIAZQBuAGQAZQByAGUAZAB9AC0AUgBFAEMAXwB7AG8AbgBzAGkAdABlAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AKQApACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMgAsAGUAbABlAGMAfQAgAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBQAFAAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABQAG8AdwBlAHIAIABQAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAAdABoAGUAIABMAGEAcgBnAGUALQBzAGMAYQBsAGUAIABSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAVABhAHIAZwBlAHQAIAAoAEwAUgBFAFQAKQBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAFIAUABQAFwAIgAsACAAXAAiAGoAdQByAGkAcwBkAGkAYwB0AGkAbwBuAGEAbAAgAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAIAAoAEEAQwBUACAAbwBuAGwAeQApAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAARQBuAGUAcgBnAHkAIABDAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHAAbwByAHQAaQBuAGcAIAB5AGUAYQByAFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBFAEMAXwBvAG4AcwBpAHQAZQBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAEUAbgBlAHIAZwB5ACAAQwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIABpAHMAcwB1AGUAZAAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAByAG8AZAB1AGMAZQBkACAAbwBuAC0AcwBpAHQAZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIAB5AGUAYQByACAAYQBuAGQAIABjAG8AbgBzAHUAbQBlAGQAIABiAHkAIAB0AGgAZQAgAGUAbgB0AGkAdAB5AFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUgBNAEYAMgBlAGwAZQBjAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADIAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAVwBoAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABJAG4AIABvAHIAZABlAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAbQBlAGcAYQB3AGEAdAB0ACAAaABvAHUAcgBzACAAdABvACAAawBpAGwAbwB3AGEAdAB0ACAAaABvAHUAcgBzACwAIAB0AGgAZQAgAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAAYQBuAGQAIABSAEUAQwBfAG8AbgBzAGkAdABlACAAdgBhAHIAaQBhAGIAbABlAHMAIABhAHIAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAGQAIABiAHkAIAAxADAAXgAzACAAaQBuAHMAdABlAGEAZAAgAG8AZgAgADEAMABeAC0AMwAuAFwAIgApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABhAHQAYQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAxAF8AXwAxAF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADEAXwBfADEAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANABfADEAXwAyAF8AXwAxAF8ATQBhAHIAawBlAHQAQgBhAHMAZQBkAFMAYwBvAHAAZQBFAGwAZQBjAHQAcgBpAGMAaQB0AHkARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA0AF8AMQBfADIAXwBfADEAXwBNAGEAcgBrAGUAdABCAGEAcwBlAGQAUwBjAG8AcABlAEUAbABlAGMAdAByAGkAYwBpAHQAeQBFAG0AaQBzAHMAaQBvAG4AcwBWAGEAcgBpAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADQAXwAxAF8AMgBfAF8AMQBfAE0AYQByAGsAZQB0AEIAYQBzAGUAZABTAGMAbwBwAGUARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -14663,22 +14646,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14697,6 +14664,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>

--- a/Excel/14_Electricity_Scope2_WIP_v02.xlsx
+++ b/Excel/14_Electricity_Scope2_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E56E0D1-1A4A-487C-8B6F-2201D91CAD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6A9B50-3FE5-4A15-8507-461AF5DA2A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2145" yWindow="2460" windowWidth="36255" windowHeight="19140" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Input - Electricity" sheetId="70" r:id="rId5"/>
     <sheet name="14.1.1-2 Purchased electricity" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Electricity" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="128" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="129" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
@@ -125,7 +125,13 @@
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Title">_xlfn.LAMBDA("Emission factor for nitrogen leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Variation">_xlfn.LAMBDA((""))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(14, 5,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
@@ -167,13 +173,25 @@
     <definedName name="Common_SourceData.Common_SourceData_GWP_Title">_xlfn.LAMBDA("Global warming potential for greenhouse gases")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Variable">_xlfn.LAMBDA("GWPN2O")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(3, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Title">_xlfn.LAMBDA("VEERG Australian leaching zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(21, 16,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.8.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Title">_xlfn.LAMBDA("Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Unit">_xlfn.LAMBDA("fraction")</definedName>
@@ -278,9 +296,15 @@
     <definedName name="Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 2a"))</definedName>
     <definedName name="Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Title">_xlfn.LAMBDA(("Electricity scope 2 and scope 3 market-based emission factors"))</definedName>
     <definedName name="Electricity_SourceData.Electricity_Scope2Scope3MarketBased_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
     <definedName name="Fertiliser_Equations_Lime.VEERG_5_3_1_1__1_LimeApplication">_xlfn.LAMBDA(_xlpm.Mlime,_xlpm.FracLime,_xlpm.Plime,_xlpm.EFlime,_xlpm.FracDol,_xlpm.Pdol,_xlpm.EFdol,_xlpm.CgCO2, ((_xlpm.Mlime * _xlpm.FracLime * _xlpm.Plime * _xlpm.EFlime) + (_xlpm.Mlime * _xlpm.FracDol * _xlpm.Pdol * _xlpm.EFdol)) * _xlpm.CgCO2 * 10 ^ -3)</definedName>
     <definedName name="Fertiliser_Equations_Organic.VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser">_xlfn.LAMBDA(_xlpm.Morganicjf,_xlpm.FNorganicf, _xlpm.Morganicjf * _xlpm.FNorganicf)</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1">'14.1.1-2 Purchased electricity'!$E$18</definedName>
     <definedName name="VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1">'14.1.1-2 Purchased electricity'!$E$39</definedName>
     <definedName name="X_Cell_Electricity_CalculationMethod">'Input - Electricity'!$E$5</definedName>
@@ -357,7 +381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="204">
   <si>
     <t>INPUTS</t>
   </si>
@@ -899,6 +923,150 @@
   </si>
   <si>
     <t>Location-based (simpler)</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Data quality scoring</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_TemporalRepresentativeness</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Data collected covers the time-period for which emissions are being estimated  </t>
+  </si>
+  <si>
+    <t>TR5</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 2 years of the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR4</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 3 years of to the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR3</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 4 years of the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR2</t>
+  </si>
+  <si>
+    <t>Age of data unknown or data more than 4 years older than the time-period being reported  </t>
+  </si>
+  <si>
+    <t>TR1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_SpatialRepresentativeness</t>
+  </si>
+  <si>
+    <t>Data covers specific entity location(s) with spatial partitioning or using stratified sampling within property </t>
+  </si>
+  <si>
+    <t>SR5</t>
+  </si>
+  <si>
+    <t>Data covers specific entity location(s) without spatial partitioning within property  </t>
+  </si>
+  <si>
+    <t>SR4</t>
+  </si>
+  <si>
+    <t>Data based on regional data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR3</t>
+  </si>
+  <si>
+    <t>Data based on state data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR2</t>
+  </si>
+  <si>
+    <t>Data based on national data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_SampleSize</t>
+  </si>
+  <si>
+    <t>Data based on sample size of &gt;90% (e.g. total annual fuel purchases) </t>
+  </si>
+  <si>
+    <t>SS5</t>
+  </si>
+  <si>
+    <t>Data based on sample size of 51-90%  </t>
+  </si>
+  <si>
+    <t>SS4</t>
+  </si>
+  <si>
+    <t>Data based on sample size of 21-50%  </t>
+  </si>
+  <si>
+    <t>SS3</t>
+  </si>
+  <si>
+    <t>Data based on sample size of &lt;20% (e.g. liveweight measured for 10% of herd) </t>
+  </si>
+  <si>
+    <t>SS2</t>
+  </si>
+  <si>
+    <t>Unknown (e.g. data based on national/state/regional data source) </t>
+  </si>
+  <si>
+    <t>SS1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_Scope3</t>
+  </si>
+  <si>
+    <t>Verified data provided by supplier consistent with ISO14067:2018 or GHG Protocol Product Lifecycle Accounting and Reporting Standard </t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Unverified supplier data, consistent with ISO14067:2018 or GHG Protocol Product Lifecycle Accounting and Reporting Standard, or consistent with these Guidelines (where appropriate)</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Regionally relevant product specific value from database developed using international best practice </t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Nationally relevant product specific value from database developed using international best practice   </t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Geographically generic product specific value from database developed using international best practice </t>
+  </si>
+  <si>
+    <t>S31</t>
   </si>
 </sst>
 </file>
@@ -1836,7 +2004,7 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2172,6 +2340,7 @@
     <xf numFmtId="0" fontId="60" fillId="9" borderId="4" xfId="34" applyFont="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="67"/>
   </cellXfs>
   <cellStyles count="70">
     <cellStyle name="Alert" xfId="59" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
@@ -2245,7 +2414,7 @@
     <cellStyle name="Variable type input" xfId="62" xr:uid="{83ED2376-8555-47B3-98E3-2416CC880284}"/>
     <cellStyle name="Variable type other" xfId="63" xr:uid="{6646F6F7-E4F9-4165-8015-E25083532B5B}"/>
   </cellStyles>
-  <dxfs count="68">
+  <dxfs count="69">
     <dxf>
       <font>
         <color rgb="FFC44340"/>
@@ -2435,6 +2604,30 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="171" formatCode="[$-C09]d\ mmmm\ yyyy;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3502,20 +3695,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="67"/>
-      <tableStyleElement type="headerRow" dxfId="66"/>
-      <tableStyleElement type="totalRow" dxfId="65"/>
-      <tableStyleElement type="firstColumn" dxfId="64"/>
-      <tableStyleElement type="firstRowStripe" dxfId="63"/>
-      <tableStyleElement type="secondRowStripe" dxfId="62"/>
+      <tableStyleElement type="wholeTable" dxfId="68"/>
+      <tableStyleElement type="headerRow" dxfId="67"/>
+      <tableStyleElement type="totalRow" dxfId="66"/>
+      <tableStyleElement type="firstColumn" dxfId="65"/>
+      <tableStyleElement type="firstRowStripe" dxfId="64"/>
+      <tableStyleElement type="secondRowStripe" dxfId="63"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="61"/>
-      <tableStyleElement type="headerRow" dxfId="60"/>
-      <tableStyleElement type="totalRow" dxfId="59"/>
-      <tableStyleElement type="firstColumn" dxfId="58"/>
-      <tableStyleElement type="firstRowStripe" dxfId="57"/>
-      <tableStyleElement type="secondRowStripe" dxfId="56"/>
+      <tableStyleElement type="wholeTable" dxfId="62"/>
+      <tableStyleElement type="headerRow" dxfId="61"/>
+      <tableStyleElement type="totalRow" dxfId="60"/>
+      <tableStyleElement type="firstColumn" dxfId="59"/>
+      <tableStyleElement type="firstRowStripe" dxfId="58"/>
+      <tableStyleElement type="secondRowStripe" dxfId="57"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -5530,16 +5723,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{7C067140-32A3-4019-BB9F-D94D581B0108}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1AB65AC6-E60A-4C37-A65E-BDFF0E02E8DF}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B088BAE6-7710-4DF8-BCE9-0D1B08F2A8D1}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{CC199480-8E5E-4B24-A151-B1DEC6A865DA}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ED24F680-2739-467B-95AB-EBB83DA1BFFE}" name="Wet or Dry Zone" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{AEE12B96-CBAD-4DFB-B435-19D91CF15C61}" name="Wet or Dry Zone" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5548,7 +5741,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{645A5184-C28E-4C9D-9CCE-2399F8562A84}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{3485604F-39EC-4E63-A0FB-C192569819B3}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5556,16 +5749,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{AB9AC30C-1502-403A-8B16-4C903DA4620D}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{E6E2671D-0A37-4446-8BA5-2CE127F561B8}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5521103E-F249-4068-84C2-BACE5EFD5B71}" name="MAT">
+    <tableColumn id="2" xr3:uid="{3AD06181-3103-4920-B125-CBE38B1E90FF}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1A5B2A0C-9FB7-4C83-BE24-2739F2EE4BBC}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{2B726B4D-9524-4FB5-AE01-945C0963233D}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{1644B56C-5210-463B-9955-0AD461E10412}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{10587017-7167-484F-A3F1-863352992573}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5574,7 +5767,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{AF3EDC5E-E2D1-49A9-AF31-977BE00CE796}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{0243CD26-B08C-4FA2-B922-BDA683621913}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5582,16 +5775,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{808E0819-272F-4F79-BB59-D537CD4147E5}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{73E0EF1E-C2ED-40CE-9264-F3AF5DCA5FD0}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E07D5C59-5E5E-4237-878D-AA0908374DB3}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{DCAF4479-6DEB-40F4-8641-46AC560D79EA}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5754235C-6C2C-42B4-92AA-AEE240F95955}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{663795C8-BF57-4218-B76F-8C6239710054}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BA3EAC27-F8CD-4F25-8819-B30FCB46CC7C}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{7E98C813-F703-4EE5-8D72-A877F898B19A}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5600,16 +5793,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{533DAE28-F4C2-48D9-ABB7-5B00FD092A05}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{4240365B-BD52-4F38-9501-5A03A9C67B97}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7200DD7F-5532-4AD8-BBF9-FA19D2C5785B}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{24606342-7318-4B88-93B6-8EDF1E856401}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{93FD9F5E-AA6E-498C-9AA2-CC9779032111}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{E1B739BE-6CE4-41F5-AE40-2BA6760E8676}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5618,16 +5811,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{E4CF6C0B-564B-424F-A169-7D59FCA2B3CA}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{E5EB0254-404E-4715-8384-90215CE30885}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2488E72E-D353-4324-AE9D-C442C4331FBF}" name="Data source">
+    <tableColumn id="1" xr3:uid="{F3485A70-CFAB-494D-A268-D4DA2C85F8F1}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F5C32B98-48FD-4261-87B4-453D9BE9E2ED}" name="Data score">
+    <tableColumn id="2" xr3:uid="{E1637489-2716-411B-AD0F-FDFBD57E4708}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5636,16 +5829,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{7CBFF4A5-8886-49EF-9F33-DCD76AE9B32A}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{7E56E3A3-B902-4F76-8140-9082CED5EB6C}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BD2D0241-FFA4-42EF-A7B9-2CB0E0DEC201}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{2D1BA0CD-9B0C-4E4C-9BA0-D3322AAA75CC}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AEC9B820-248B-4B84-96A9-0CB02F4FF2AA}" name="FracWET" dataDxfId="39">
+    <tableColumn id="2" xr3:uid="{5682452E-BA64-4434-8F18-F2F707FE01E1}" name="FracWET" dataDxfId="40">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5654,7 +5847,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{611E2A5E-657D-43DF-AB62-A1CD4CA0C888}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B90F025E-B512-4A7C-9D7C-7C8C96CA2CD4}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5663,19 +5856,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{552423E4-4B33-44EB-B4BD-3B8BD118AC9B}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{838379B7-035D-4BFC-ADC4-36A59837C5B7}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BB728903-2B86-4F84-A7DC-85309CFFECF2}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{6458D9E3-5B14-4596-AA53-36D4DA9C64DA}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0EA81DC0-4AD6-4847-A018-E6FFA14025AC}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{632B69E9-229B-4185-B520-1E18E838E1B2}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6119E9D6-697F-45F3-9A0E-F8C0924FDC27}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{8A3C03EA-DAE5-468F-ABF5-79BA64014CCA}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7E670E63-B90E-4E76-BED2-C10863007BCA}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{3B09CC97-8437-439E-B18B-B7155430BA24}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5684,16 +5877,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{97DC09EA-3F9A-45F1-8271-976FC0C10458}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{19547F07-ED2F-4E93-A359-E018D5843E39}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7AF64C62-0AB6-4E97-AC00-03D00A62ED3D}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{0E733206-E30D-4D27-B4CD-E0D3A8E5FD8C}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{34CAEC98-1032-45D6-9D51-DA9260C5AED3}" name="FracWET" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{EF46D247-7FED-45B8-90A0-EFA9C208138A}" name="FracWET" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5702,16 +5895,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{54A156B6-993A-4AC9-9D39-6F67361EC731}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{9A8BB662-ACF8-4F65-970D-75F17CC92875}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B6D77EBA-360C-4CDF-9614-9DBBA42D2BB0}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{7C076B9D-5D90-4872-96B9-2B933426DE96}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B0E51103-7E63-4EE2-AF8E-41F32599E6CA}" name="EFPRP" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{48F5A9F9-B3C7-4774-B2D2-EDEB1E772DC9}" name="EFPRP" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5720,16 +5913,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{AE1DE019-0A34-4762-99C4-D21E295B23F1}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{81C9A78D-5D6D-4F1E-AC3D-3BD2EEC0A528}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D8A2B127-4200-46FC-A53B-C560147D65A2}" name="Month">
+    <tableColumn id="1" xr3:uid="{B47FBA50-26A9-479F-A3EC-26DC561F8BBE}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{360953E6-AC1A-4E0B-8B98-D3657D507C05}" name="Season" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C224C799-9F00-4316-A715-A7951D80F5A5}" name="Season" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5766,7 +5959,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{75B85262-003F-4B20-8577-B48CE5235BD6}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{ED2C821D-CEA2-457E-B062-2E77211056E6}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5786,52 +5979,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{861DBD89-9B55-4023-96AB-B54A6C6EA4BC}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{B328342E-29C6-46AB-BB34-41BA7E434D8D}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FAC9547C-A240-4811-97C7-6C4CCAF05D98}" name="MAT (ºC)" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7192C847-87B4-40FA-AF4D-5CDED5CF9054}" name="MAT (ºC)" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{500792E9-FF69-4654-AB53-6218F1DB0676}" name="Anaerobic lagoon" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{5597500E-37BE-4745-AFB2-0BFBCD34912F}" name="Anaerobic lagoon" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{325C5524-B036-43DD-8A85-F0D3D7922182}" name="Digester / covered lagoons" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{23B61021-7A85-4B5E-9B44-A963713F96E6}" name="Digester / covered lagoons" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{58AABE7A-A73E-429F-8993-05E0EFFEE698}" name="Liquid systems" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{F32A8C1E-593B-4E2E-99EF-9D39F0CC5082}" name="Liquid systems" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E114649C-1BEC-4319-838D-3F2DD4A83E94}" name="Daily spread" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{DDFD927E-C2EF-436B-9355-9EF84AA89075}" name="Daily spread" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B80B29E1-DB25-4930-8D66-EC59FDFA88F6}" name="Composting (passive windrow)" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{B759C93D-8DD7-47BB-BBBB-DA79891494B1}" name="Composting (passive windrow)" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A11E2C6B-8A71-4622-8480-5043E8FC12A7}" name="Solid storage" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{819C6E5D-61ED-4114-9501-28E4A98FEA2B}" name="Solid storage" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F9D9E7C3-C119-48EC-A3A3-E52AA592857C}" name="Pit storage" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{82943E7E-1360-4526-9CD2-5FE6599B5B84}" name="Pit storage" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FB5BBE2C-1F5F-471B-8C5B-3BF51A301F26}" name="Deep litter" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{C55197FB-5F11-453D-834A-D31E564BBF17}" name="Deep litter" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{997FB6AD-5F85-4931-B3D2-205EF6077EB2}" name="Poultry manure with bedding" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{9C07C536-570C-4F1F-9A8F-A774E0BCDBD9}" name="Poultry manure with bedding" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{C1DBBC95-232F-4C60-884F-8409E757871F}" name="Poultry manure without bedding" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{0614667E-C6B3-4AB1-B98A-5AFE082541A4}" name="Poultry manure without bedding" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{07BFF041-6262-4E72-A014-EC5417657D6B}" name="Direct processing" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{A753372C-B18B-433B-A530-092C07E8C107}" name="Direct processing" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{DB6394D4-A471-4D18-86B5-809AE59820F0}" name="Direct application" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{E08B785A-2C08-4D11-9145-74C4B5F623EC}" name="Direct application" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{850F0B7D-6541-44AD-B7B9-2D9A44E1F289}" name="Pasture range and paddock" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{49C77BD5-954F-4D1C-AB42-B5E11901B157}" name="Pasture range and paddock" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{2A46A6F7-2F25-4EE9-BC06-43F9FB1B4FE1}" name="MAT raw" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{F7197D57-B19F-47D3-AC2B-409A610EA5A6}" name="MAT raw" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5840,18 +6033,82 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{80FF0002-A042-450B-BE79-58C0DE6DE3C9}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{42BB21BB-C495-41A5-A34B-EB070DCDF52E}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4E536E2D-59CB-407B-99E7-0996C3C53800}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{71227CE2-937F-487C-9F9E-D8FDF1C3FA26}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7B0CA143-FD75-4586-845D-12D6AC370D90}" name="EFNi &amp; EFN2Oi" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{33B689C8-0B0A-463E-807F-69AB38F05392}" name="EFNi &amp; EFN2Oi" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{F44A4FD6-B7C3-4727-BEFA-910ED1FA96D2}" name="Table_SourceData_DataQuality_TemporalRepresentativeness" displayName="Table_SourceData_DataQuality_TemporalRepresentativeness" ref="D265:F270" totalsRowShown="0">
+  <autoFilter ref="D265:F270" xr:uid="{9AD44602-D2F2-4D97-923C-A32E98F8C17A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="2" xr3:uid="{A39113CF-8DA3-4F59-837D-7CF5B92D3D20}" name="Description" dataDxfId="20" dataCellStyle="Content normal"/>
+    <tableColumn id="1" xr3:uid="{5E0AFAE9-22AD-4E0D-9B0F-00054267ABB7}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{D1A9D0C7-7C2E-4E33-A1E9-95756C4B6202}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{1439B1AA-217D-4A19-B6E3-6C8EAD03FE20}" name="Table_SourceData_DataQuality_SpatialRepresentativeness" displayName="Table_SourceData_DataQuality_SpatialRepresentativeness" ref="D274:F279" totalsRowShown="0">
+  <autoFilter ref="D274:F279" xr:uid="{95094D65-3E0E-45CE-A3F4-F41E74C11901}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{87F924A7-786C-484A-8FC6-EBF1D159405E}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{93D02419-4DA8-4D93-8D4C-CD1744BE84E4}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{5E336AD9-E422-48B5-83B3-738C98B2BC48}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{B707D354-6E67-428A-9020-8F60FC7F6A34}" name="Table_SourceData_DataQuality_SampleSize" displayName="Table_SourceData_DataQuality_SampleSize" ref="D283:F288" totalsRowShown="0">
+  <autoFilter ref="D283:F288" xr:uid="{DE8F748C-E65A-4AA2-81BB-D28A432CF334}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{6337BA90-59CD-4D99-9E66-674141EA0E0F}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{7638E5F9-64A2-4572-A186-B37E113802BC}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{8DD3C01C-3746-4B1B-BEF4-3D4230B2768D}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{27072D7A-DA92-42BD-B8BF-490CFBD74336}" name="Table_SourceData_DataQuality_Scope3" displayName="Table_SourceData_DataQuality_Scope3" ref="D292:F297" totalsRowShown="0">
+  <autoFilter ref="D292:F297" xr:uid="{43A1C4DA-75D1-45DF-BA9A-1798C2CC5A4B}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{3DAFA80B-941A-43A6-9246-ECE8946D7810}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{F0C88F17-3F54-4446-B854-751CDB9CE4C8}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{C3FB2B1B-78E2-440B-9F3B-DDF3B8CE91CC}" name="Score"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5910,20 +6167,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C39A165F-9435-414B-BD76-43B177ABA893}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7277BD0F-67A7-484C-BB97-A1842D68C4DF}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BE71C241-61E8-4489-AA76-96443EAE034C}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{06FB737B-43E7-4887-93B2-F4E751669EB5}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ACC3E50D-CE1E-459D-B928-9CDE4A67A1A2}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{58BDCA68-2A4B-45A6-A420-B41CF6D2528B}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{86CD3F57-A5E1-461A-9440-621D09F09F3C}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{7F13E03E-FAA2-4B14-9BCD-E83A25AF4C12}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5932,12 +6189,12 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{B4DA963B-8478-4AB1-8F1D-C1E8EAAA9347}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4273BE33-77F0-4C6F-915A-1FC540C3851E}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{0070E606-E49D-4FE4-85EA-C0B588C6C39D}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{52825734-19C7-4C58-BF6D-9EDB6217103B}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5946,16 +6203,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{1BC3B980-BCF0-45EA-B194-1A23812AB71E}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{7CD8100A-CC82-40C8-AF1E-71BF154A717A}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{47C418B3-C9EA-4555-91DE-E1FF1A90A524}" name="Gas">
+    <tableColumn id="1" xr3:uid="{B0CE9877-E096-4209-8175-BA898B027680}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{28631823-8572-452C-B0CD-79BB1E4EB905}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{CD24392D-4F25-4ECB-9398-F02742ED25F0}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5964,7 +6221,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E324FC9B-368F-45A3-88F6-211F7A1F5446}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{AC0EB8BB-59AC-4EC8-8148-D1348263C77D}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5973,19 +6230,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7E0102E5-39C7-467E-ABA3-6D7448E15909}" name="Gas">
+    <tableColumn id="1" xr3:uid="{2E9F6955-7FD4-47D8-AE2C-0C5804E57DE9}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{305B303B-E0BD-401D-A43D-46BB79576AF1}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{6364FB75-C03A-41BF-9088-26D95A2899E6}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BD313F47-C67B-4A2C-8D04-6EC8BAE84EB6}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{F8865B13-18A9-4F2C-8978-86B6BA6BBFA1}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{71A4A22E-A47E-4205-911D-095C78950B96}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{C301EFFC-7ABA-4419-888D-AC2DF6EDB915}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{1B92919E-EEA8-4C10-BB85-04B4E14093ED}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{E17C081C-FBA8-4890-BF1E-8D5BA2F5D525}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5994,7 +6251,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F578B290-90D6-446E-9DB8-A202D56AF960}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{322C3680-D8C4-4C25-97D5-FECC09937A13}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6014,52 +6271,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{96A5F01C-5883-41AF-AE28-D50B33672E80}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{BE7EA1D8-3EBA-442D-AB6F-EA21F9486684}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{041A7D61-1145-47CF-9231-81A191C5F525}" name="MAT" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{DD09788D-F50D-489D-806B-21B16C717626}" name="MAT" totalsRowDxfId="56" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{71DB1B83-1EF9-4634-964A-C956AA7AF679}" name="MAP" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{B1E36F24-514C-40E3-9C39-9F147E9C0DA5}" name="MAP" totalsRowDxfId="55" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{89E58885-C79C-49DA-BAE3-148D2762C05E}" name="Frost days per year" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{2D907057-B652-4E18-97C4-035A84ADA318}" name="Frost days per year" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{56C31162-3402-4F22-95BA-6A91114DC55B}" name="Elevation" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{2175178D-6969-4BA8-9AAE-EAB13542C75C}" name="Elevation" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{31F74135-44AD-4F36-A2FD-80E1F0FB4D15}" name="MAP:PET" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{CC5DF494-8FC1-434C-9EAA-99DB74D32902}" name="MAP:PET" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2E0B3AA9-CA2C-4B68-ADB0-8647555F7F49}" name="Min temp" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{357BDBCF-EAA2-40C6-9ECA-B615D727EC67}" name="Min temp" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{07EDCFA0-D219-4138-BA2B-806B1E51A6AE}" name="Max temp" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{4A5DE9E5-152B-4FD9-8433-EF34639B9F59}" name="Max temp" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{21F92A33-0D75-45A5-B10A-7B2610BF71B3}" name="Min rainfall" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{4E15C4F1-87F0-418A-87D0-B1FBB3FC8170}" name="Min rainfall" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2C70F876-426D-42B1-AEF9-6165CF598743}" name="Max rainfall" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{D6024659-185F-4605-8747-5EE4D501CBC6}" name="Max rainfall" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{B9045312-700F-40E5-9187-039E98B47579}" name="Min frost days" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{16423147-57E7-456C-9B50-9C2D2652AE04}" name="Min frost days" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{154F16DB-03E0-4224-AE8B-7CBF1AF45931}" name="Max frost days" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{D75E0E99-3DAC-403F-9558-3DF7897E3EA8}" name="Max frost days" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{A9EFE373-8085-4335-BF5F-94DEC1E07441}" name="Min elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{C3635C89-287E-421A-9C4D-7CB10C17AF70}" name="Min elevation" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{B3504ADE-D373-42DE-8048-5A75D80484B7}" name="Max elevation" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{832E6E8F-9E07-4471-A3F0-DFA65D6323E0}" name="Max elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{99152ED2-293E-4DC8-B70A-7732306119EB}" name="Min MAP:PET" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{76F78897-620D-4038-ACED-FA50EC9BD18B}" name="Min MAP:PET" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{AE69E55F-A5CE-4821-9A38-0C899BF6270E}" name="Max MAP:PET" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{F9132809-851C-46E3-A288-359890E3CF4C}" name="Max MAP:PET" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6322,75 +6579,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CF26AA-F4FA-460F-9B3A-C19960195F0B}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="str">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="120" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="str">
-        <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
-        <v>Overview</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="str">
-        <f>HYPERLINK("#'Results'!A1", "Results")</f>
-        <v>Results</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="str">
-        <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
-        <v>Site</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="str">
-        <f>HYPERLINK("#'Input - Electricity'!A1", "Electricity")</f>
-        <v>Electricity</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="str">
-        <f>HYPERLINK("#'14.1.1-2 Purchased electricity'!A1", "14.1.1-2 Purchased electricity")</f>
-        <v>14.1.1-2 Purchased electricity</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="119" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="119" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="str">
-        <f>HYPERLINK("#'Constants - Electricity'!A1", "Constants - Electricity")</f>
-        <v>Constants - Electricity</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="str">
+    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="str">
+        <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
+        <v>Acknowledgements</v>
       </c>
     </row>
   </sheetData>
@@ -10264,8 +10481,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4545C4-0913-41FB-A369-8BB7C067FCFB}">
-  <dimension ref="A1:BY259"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C043D4B-AFFF-46A8-A351-BC425846ECB2}">
+  <sheetPr>
+    <tabColor theme="2" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:BY297"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="7" customWidth="1"/>
@@ -10292,7 +10512,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:65" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="e" vm="1">
+      <c r="A1" s="8" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
@@ -10330,17 +10550,11 @@
       <c r="W3" s="10"/>
     </row>
     <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="str">
-        <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
-        <v>Overview</v>
-      </c>
+      <c r="A4"/>
       <c r="BM4" s="3"/>
     </row>
     <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="str">
-        <f>HYPERLINK("#'Results'!A1", "Results")</f>
-        <v>Results</v>
-      </c>
+      <c r="A5"/>
       <c r="D5" s="6" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
         <v>Australian states and territories</v>
@@ -10348,7 +10562,9 @@
       <c r="BM5" s="3"/>
     </row>
     <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6"/>
+      <c r="A6" s="119" t="s">
+        <v>1</v>
+      </c>
       <c r="D6" s="26" t="s">
         <v>5</v>
       </c>
@@ -10360,7 +10576,10 @@
       </c>
     </row>
     <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7"/>
+      <c r="A7" s="57" t="str">
+        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
+        <v>Constants - Common</v>
+      </c>
       <c r="D7" s="26" t="str" cm="1">
         <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>New South Wales</v>
@@ -10375,8 +10594,9 @@
       </c>
     </row>
     <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>0</v>
+      <c r="A8" s="14" t="str">
+        <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
+        <v>Acknowledgements</v>
       </c>
       <c r="D8" s="26" t="str" cm="1">
         <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10392,10 +10612,7 @@
       </c>
     </row>
     <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="str">
-        <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
-        <v>Site</v>
-      </c>
+      <c r="A9"/>
       <c r="D9" s="26" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Victoria</v>
@@ -10410,10 +10627,7 @@
       </c>
     </row>
     <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="str">
-        <f>HYPERLINK("#'Input - Electricity'!A1", "Electricity")</f>
-        <v>Electricity</v>
-      </c>
+      <c r="A10"/>
       <c r="D10" s="26" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Queensland</v>
@@ -10460,9 +10674,7 @@
       <c r="BM12" s="3"/>
     </row>
     <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>44</v>
-      </c>
+      <c r="A13"/>
       <c r="D13" s="26" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Tasmania</v>
@@ -10477,10 +10689,7 @@
       </c>
     </row>
     <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="str">
-        <f>HYPERLINK("#'14.1.1-2 Purchased electricity'!A1", "14.1.1-2 Purchased electricity")</f>
-        <v>14.1.1-2 Purchased electricity</v>
-      </c>
+      <c r="A14"/>
       <c r="D14" s="26" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Northern Territory</v>
@@ -10501,25 +10710,17 @@
       <c r="A16"/>
     </row>
     <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="119" t="s">
-        <v>1</v>
-      </c>
+      <c r="A17"/>
     </row>
     <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="str">
-        <f>HYPERLINK("#'Constants - Electricity'!A1", "Constants - Electricity")</f>
-        <v>Constants - Electricity</v>
-      </c>
+      <c r="A18"/>
       <c r="D18" s="6" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="str">
-        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
-        <v>Constants - Common</v>
-      </c>
+      <c r="A19"/>
       <c r="D19" s="5" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
@@ -14373,7 +14574,7 @@
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D257" s="26" t="s">
         <v>77</v>
       </c>
@@ -14381,7 +14582,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D258" s="26" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -14391,7 +14592,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -14401,10 +14602,299 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
+    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D263" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D264" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D265" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E265" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F265" s="26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D266" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E266" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="F266" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D267" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="E267" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="F267" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D268" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="E268" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="F268" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D269" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="E269" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="F269" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D270" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="E270" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="F270" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D273" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D274" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E274" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F274" s="26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D275" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="E275" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="F275" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D276" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="E276" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="F276" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D277" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="E277" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="F277" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D278" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="E278" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="F278" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D279" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="E279" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="F279" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D282" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D283" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E283" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F283" s="26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D284" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="E284" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="F284" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D285" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E285" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="F285" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D286" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="E286" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="F286" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D287" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="E287" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="F287" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D288" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="E288" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="F288" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D291" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D292" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E292" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F292" s="26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D293" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="E293" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="F293" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D294" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="E294" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="F294" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D295" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="E295" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F295" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D296" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="E296" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="F296" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D297" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="E297" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="F297" s="26">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="17">
+  <tableParts count="21">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -14422,6 +14912,10 @@
     <tablePart r:id="rId16"/>
     <tablePart r:id="rId17"/>
     <tablePart r:id="rId18"/>
+    <tablePart r:id="rId19"/>
+    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId21"/>
+    <tablePart r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14622,7 +15116,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgAC